--- a/docs/reports/MU.xlsx
+++ b/docs/reports/MU.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Model" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SWS Valuation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target Price" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Model" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="6" state="visible" r:id="rId6"/>
@@ -144,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -160,20 +160,16 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -183,6 +179,7 @@
     <xf numFmtId="165" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -570,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Technology · Standard (2-Stage FCFE) · generated 2026-07-09 · data: yfinance</t>
+          <t>Technology · Standard (forward multiples + DCF) · generated 2026-10-13 · data: Yahoo snapshot as of 2026-07-09</t>
         </is>
       </c>
     </row>
@@ -588,7 +585,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DCF value per share</t>
+          <t>DCF value per share (one lens)</t>
         </is>
       </c>
       <c r="B5" s="4">
@@ -610,11 +607,11 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Blended fair value (report)</t>
+          <t>12-month price target (report)</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>34784.0660543677</v>
+        <v>1264.833590981985</v>
       </c>
     </row>
     <row r="8">
@@ -702,7 +699,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As reported by yfinance (USDmm). Hardcoded actuals.</t>
+          <t>As reported by Yahoo snapshot as of 2026-07-09 (USDmm). Hardcoded actuals.</t>
         </is>
       </c>
     </row>
@@ -744,16 +741,16 @@
           <t>Treasury Shares Number</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="25" t="n">
         <v>132</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>141</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="25" t="n">
         <v>144</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="25" t="n">
         <v>144</v>
       </c>
     </row>
@@ -763,16 +760,16 @@
           <t>Ordinary Shares Number</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="25" t="n">
         <v>1094</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="25" t="n">
         <v>1098</v>
       </c>
-      <c r="E6" s="29" t="n">
+      <c r="E6" s="25" t="n">
         <v>1108.841326</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="25" t="n">
         <v>1122</v>
       </c>
     </row>
@@ -782,16 +779,16 @@
           <t>Share Issued</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="25" t="n">
         <v>1226</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="25" t="n">
         <v>1239</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="25" t="n">
         <v>1252.841326</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="25" t="n">
         <v>1266</v>
       </c>
     </row>
@@ -801,13 +798,13 @@
           <t>Net Debt</t>
         </is>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="25" t="n">
         <v>3472</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="25" t="n">
         <v>4302</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="25" t="n">
         <v>1891</v>
       </c>
     </row>
@@ -817,16 +814,16 @@
           <t>Total Debt</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>7516</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>13933</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="25" t="n">
         <v>14007</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="25" t="n">
         <v>15278</v>
       </c>
     </row>
@@ -836,16 +833,16 @@
           <t>Tangible Book Value</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="25" t="n">
         <v>48258</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="25" t="n">
         <v>42566</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="25" t="n">
         <v>43565</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="25" t="n">
         <v>52562</v>
       </c>
     </row>
@@ -855,16 +852,16 @@
           <t>Invested Capital</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="25" t="n">
         <v>55927</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="25" t="n">
         <v>56169</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="25" t="n">
         <v>56474</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="25" t="n">
         <v>65698</v>
       </c>
     </row>
@@ -874,16 +871,16 @@
           <t>Working Capital</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>14242</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>16479</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="25" t="n">
         <v>15124</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="25" t="n">
         <v>17387</v>
       </c>
     </row>
@@ -893,16 +890,16 @@
           <t>Net Tangible Assets</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>48258</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>42566</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="25" t="n">
         <v>43565</v>
       </c>
-      <c r="F13" s="29" t="n">
+      <c r="F13" s="25" t="n">
         <v>52562</v>
       </c>
     </row>
@@ -912,16 +909,16 @@
           <t>Capital Lease Obligations</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="25" t="n">
         <v>1496</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="25" t="n">
         <v>1884</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="25" t="n">
         <v>2664</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="25" t="n">
         <v>3745</v>
       </c>
     </row>
@@ -931,16 +928,16 @@
           <t>Common Stock Equity</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="25" t="n">
         <v>49907</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="25" t="n">
         <v>44120</v>
       </c>
-      <c r="E15" s="29" t="n">
+      <c r="E15" s="25" t="n">
         <v>45131</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="25" t="n">
         <v>54165</v>
       </c>
     </row>
@@ -950,16 +947,16 @@
           <t>Total Capitalization</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="25" t="n">
         <v>55927</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="25" t="n">
         <v>56063</v>
       </c>
-      <c r="E16" s="29" t="n">
+      <c r="E16" s="25" t="n">
         <v>56368</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="25" t="n">
         <v>65698</v>
       </c>
     </row>
@@ -969,16 +966,16 @@
           <t>Total Equity Gross Minority Interest</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="25" t="n">
         <v>49907</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="25" t="n">
         <v>44120</v>
       </c>
-      <c r="E17" s="29" t="n">
+      <c r="E17" s="25" t="n">
         <v>45131</v>
       </c>
-      <c r="F17" s="29" t="n">
+      <c r="F17" s="25" t="n">
         <v>54165</v>
       </c>
     </row>
@@ -988,16 +985,16 @@
           <t>Stockholders Equity</t>
         </is>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="25" t="n">
         <v>49907</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="25" t="n">
         <v>44120</v>
       </c>
-      <c r="E18" s="29" t="n">
+      <c r="E18" s="25" t="n">
         <v>45131</v>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="25" t="n">
         <v>54165</v>
       </c>
     </row>
@@ -1007,16 +1004,16 @@
           <t>Gains Losses Not Affecting Retained Earnings</t>
         </is>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="25" t="n">
         <v>-560</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="25" t="n">
         <v>-312</v>
       </c>
-      <c r="E19" s="29" t="n">
+      <c r="E19" s="25" t="n">
         <v>-134</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="25" t="n">
         <v>-32</v>
       </c>
     </row>
@@ -1026,16 +1023,16 @@
           <t>Other Equity Adjustments</t>
         </is>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="25" t="n">
         <v>-560</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="25" t="n">
         <v>-312</v>
       </c>
-      <c r="E20" s="29" t="n">
+      <c r="E20" s="25" t="n">
         <v>-134</v>
       </c>
-      <c r="F20" s="29" t="n">
+      <c r="F20" s="25" t="n">
         <v>-32</v>
       </c>
     </row>
@@ -1045,16 +1042,16 @@
           <t>Treasury Stock</t>
         </is>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="25" t="n">
         <v>7127</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="25" t="n">
         <v>7552</v>
       </c>
-      <c r="E21" s="29" t="n">
+      <c r="E21" s="25" t="n">
         <v>7852</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="25" t="n">
         <v>7852</v>
       </c>
     </row>
@@ -1064,16 +1061,16 @@
           <t>Retained Earnings</t>
         </is>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="25" t="n">
         <v>47274</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="25" t="n">
         <v>40824</v>
       </c>
-      <c r="E22" s="29" t="n">
+      <c r="E22" s="25" t="n">
         <v>40877</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="25" t="n">
         <v>48583</v>
       </c>
     </row>
@@ -1083,16 +1080,16 @@
           <t>Additional Paid In Capital</t>
         </is>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="25" t="n">
         <v>10197</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="25" t="n">
         <v>11036</v>
       </c>
-      <c r="E23" s="29" t="n">
+      <c r="E23" s="25" t="n">
         <v>12115</v>
       </c>
-      <c r="F23" s="29" t="n">
+      <c r="F23" s="25" t="n">
         <v>13339</v>
       </c>
     </row>
@@ -1102,16 +1099,16 @@
           <t>Capital Stock</t>
         </is>
       </c>
-      <c r="C24" s="29" t="n">
+      <c r="C24" s="25" t="n">
         <v>123</v>
       </c>
-      <c r="D24" s="29" t="n">
+      <c r="D24" s="25" t="n">
         <v>124</v>
       </c>
-      <c r="E24" s="29" t="n">
+      <c r="E24" s="25" t="n">
         <v>125</v>
       </c>
-      <c r="F24" s="29" t="n">
+      <c r="F24" s="25" t="n">
         <v>127</v>
       </c>
     </row>
@@ -1121,16 +1118,16 @@
           <t>Common Stock</t>
         </is>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="25" t="n">
         <v>123</v>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="25" t="n">
         <v>124</v>
       </c>
-      <c r="E25" s="29" t="n">
+      <c r="E25" s="25" t="n">
         <v>125</v>
       </c>
-      <c r="F25" s="29" t="n">
+      <c r="F25" s="25" t="n">
         <v>127</v>
       </c>
     </row>
@@ -1140,16 +1137,16 @@
           <t>Total Liabilities Net Minority Interest</t>
         </is>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="25" t="n">
         <v>16376</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="25" t="n">
         <v>20134</v>
       </c>
-      <c r="E26" s="29" t="n">
+      <c r="E26" s="25" t="n">
         <v>24285</v>
       </c>
-      <c r="F26" s="29" t="n">
+      <c r="F26" s="25" t="n">
         <v>28633</v>
       </c>
     </row>
@@ -1159,16 +1156,16 @@
           <t>Total Non Current Liabilities Net Minority Interest</t>
         </is>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="25" t="n">
         <v>8837</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="25" t="n">
         <v>15369</v>
       </c>
-      <c r="E27" s="29" t="n">
+      <c r="E27" s="25" t="n">
         <v>15037</v>
       </c>
-      <c r="F27" s="29" t="n">
+      <c r="F27" s="25" t="n">
         <v>17179</v>
       </c>
     </row>
@@ -1178,16 +1175,16 @@
           <t>Other Non Current Liabilities</t>
         </is>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="25" t="n">
         <v>835</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="25" t="n">
         <v>987</v>
       </c>
-      <c r="E28" s="29" t="n">
+      <c r="E28" s="25" t="n">
         <v>911</v>
       </c>
-      <c r="F28" s="29" t="n">
+      <c r="F28" s="25" t="n">
         <v>1443</v>
       </c>
     </row>
@@ -1197,16 +1194,16 @@
           <t>Non Current Deferred Liabilities</t>
         </is>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="25" t="n">
         <v>589</v>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="25" t="n">
         <v>727</v>
       </c>
-      <c r="E29" s="29" t="n">
+      <c r="E29" s="25" t="n">
         <v>550</v>
       </c>
-      <c r="F29" s="29" t="n">
+      <c r="F29" s="25" t="n">
         <v>1018</v>
       </c>
     </row>
@@ -1216,16 +1213,16 @@
           <t>Non Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="25" t="n">
         <v>589</v>
       </c>
-      <c r="D30" s="29" t="n">
+      <c r="D30" s="25" t="n">
         <v>727</v>
       </c>
-      <c r="E30" s="29" t="n">
+      <c r="E30" s="25" t="n">
         <v>550</v>
       </c>
-      <c r="F30" s="29" t="n">
+      <c r="F30" s="25" t="n">
         <v>1018</v>
       </c>
     </row>
@@ -1235,16 +1232,16 @@
           <t>Long Term Debt And Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="25" t="n">
         <v>7413</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="25" t="n">
         <v>13655</v>
       </c>
-      <c r="E31" s="29" t="n">
+      <c r="E31" s="25" t="n">
         <v>13576</v>
       </c>
-      <c r="F31" s="29" t="n">
+      <c r="F31" s="25" t="n">
         <v>14718</v>
       </c>
     </row>
@@ -1254,16 +1251,16 @@
           <t>Long Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="C32" s="29" t="n">
+      <c r="C32" s="25" t="n">
         <v>1393</v>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D32" s="25" t="n">
         <v>1712</v>
       </c>
-      <c r="E32" s="29" t="n">
+      <c r="E32" s="25" t="n">
         <v>2339</v>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F32" s="25" t="n">
         <v>3185</v>
       </c>
     </row>
@@ -1273,16 +1270,16 @@
           <t>Long Term Debt</t>
         </is>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="25" t="n">
         <v>6020</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="25" t="n">
         <v>11943</v>
       </c>
-      <c r="E33" s="29" t="n">
+      <c r="E33" s="25" t="n">
         <v>11237</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="25" t="n">
         <v>11533</v>
       </c>
     </row>
@@ -1292,16 +1289,16 @@
           <t>Current Liabilities</t>
         </is>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="25" t="n">
         <v>7539</v>
       </c>
-      <c r="D34" s="29" t="n">
+      <c r="D34" s="25" t="n">
         <v>4765</v>
       </c>
-      <c r="E34" s="29" t="n">
+      <c r="E34" s="25" t="n">
         <v>9248</v>
       </c>
-      <c r="F34" s="29" t="n">
+      <c r="F34" s="25" t="n">
         <v>11454</v>
       </c>
     </row>
@@ -1311,16 +1308,16 @@
           <t>Other Current Liabilities</t>
         </is>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="25" t="n">
         <v>1346</v>
       </c>
-      <c r="D35" s="29" t="n">
+      <c r="D35" s="25" t="n">
         <v>529</v>
       </c>
-      <c r="E35" s="29" t="n">
+      <c r="E35" s="25" t="n">
         <v>1518</v>
       </c>
-      <c r="F35" s="29" t="n">
+      <c r="F35" s="25" t="n">
         <v>1245</v>
       </c>
     </row>
@@ -1330,16 +1327,16 @@
           <t>Current Debt And Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="25" t="n">
         <v>103</v>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D36" s="25" t="n">
         <v>278</v>
       </c>
-      <c r="E36" s="29" t="n">
+      <c r="E36" s="25" t="n">
         <v>431</v>
       </c>
-      <c r="F36" s="29" t="n">
+      <c r="F36" s="25" t="n">
         <v>560</v>
       </c>
     </row>
@@ -1349,16 +1346,16 @@
           <t>Current Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="C37" s="29" t="n">
+      <c r="C37" s="25" t="n">
         <v>103</v>
       </c>
-      <c r="D37" s="29" t="n">
+      <c r="D37" s="25" t="n">
         <v>172</v>
       </c>
-      <c r="E37" s="29" t="n">
+      <c r="E37" s="25" t="n">
         <v>325</v>
       </c>
-      <c r="F37" s="29" t="n">
+      <c r="F37" s="25" t="n">
         <v>560</v>
       </c>
     </row>
@@ -1368,13 +1365,13 @@
           <t>Current Debt</t>
         </is>
       </c>
-      <c r="B38" s="29" t="n">
+      <c r="B38" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D38" s="25" t="n">
         <v>106</v>
       </c>
-      <c r="E38" s="29" t="n">
+      <c r="E38" s="25" t="n">
         <v>106</v>
       </c>
     </row>
@@ -1384,13 +1381,13 @@
           <t>Other Current Borrowings</t>
         </is>
       </c>
-      <c r="B39" s="29" t="n">
+      <c r="B39" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="29" t="n">
+      <c r="D39" s="25" t="n">
         <v>106</v>
       </c>
-      <c r="E39" s="29" t="n">
+      <c r="E39" s="25" t="n">
         <v>106</v>
       </c>
     </row>
@@ -1400,7 +1397,7 @@
           <t>Current Notes Payable</t>
         </is>
       </c>
-      <c r="B40" s="29" t="n">
+      <c r="B40" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1410,16 +1407,16 @@
           <t>Payables And Accrued Expenses</t>
         </is>
       </c>
-      <c r="C41" s="29" t="n">
+      <c r="C41" s="25" t="n">
         <v>6090</v>
       </c>
-      <c r="D41" s="29" t="n">
+      <c r="D41" s="25" t="n">
         <v>3958</v>
       </c>
-      <c r="E41" s="29" t="n">
+      <c r="E41" s="25" t="n">
         <v>7299</v>
       </c>
-      <c r="F41" s="29" t="n">
+      <c r="F41" s="25" t="n">
         <v>9649</v>
       </c>
     </row>
@@ -1429,16 +1426,16 @@
           <t>Current Accrued Expenses</t>
         </is>
       </c>
-      <c r="C42" s="29" t="n">
+      <c r="C42" s="25" t="n">
         <v>1358</v>
       </c>
-      <c r="D42" s="29" t="n">
+      <c r="D42" s="25" t="n">
         <v>747</v>
       </c>
-      <c r="E42" s="29" t="n">
+      <c r="E42" s="25" t="n">
         <v>1430</v>
       </c>
-      <c r="F42" s="29" t="n">
+      <c r="F42" s="25" t="n">
         <v>1498</v>
       </c>
     </row>
@@ -1448,16 +1445,16 @@
           <t>Payables</t>
         </is>
       </c>
-      <c r="C43" s="29" t="n">
+      <c r="C43" s="25" t="n">
         <v>4732</v>
       </c>
-      <c r="D43" s="29" t="n">
+      <c r="D43" s="25" t="n">
         <v>3211</v>
       </c>
-      <c r="E43" s="29" t="n">
+      <c r="E43" s="25" t="n">
         <v>5869</v>
       </c>
-      <c r="F43" s="29" t="n">
+      <c r="F43" s="25" t="n">
         <v>8151</v>
       </c>
     </row>
@@ -1467,16 +1464,16 @@
           <t>Other Payable</t>
         </is>
       </c>
-      <c r="C44" s="29" t="n">
+      <c r="C44" s="25" t="n">
         <v>2170</v>
       </c>
-      <c r="D44" s="29" t="n">
+      <c r="D44" s="25" t="n">
         <v>1419</v>
       </c>
-      <c r="E44" s="29" t="n">
+      <c r="E44" s="25" t="n">
         <v>2925</v>
       </c>
-      <c r="F44" s="29" t="n">
+      <c r="F44" s="25" t="n">
         <v>4391</v>
       </c>
     </row>
@@ -1486,16 +1483,16 @@
           <t>Total Tax Payable</t>
         </is>
       </c>
-      <c r="C45" s="29" t="n">
+      <c r="C45" s="25" t="n">
         <v>420</v>
       </c>
-      <c r="D45" s="29" t="n">
+      <c r="D45" s="25" t="n">
         <v>67</v>
       </c>
-      <c r="E45" s="29" t="n">
+      <c r="E45" s="25" t="n">
         <v>218</v>
       </c>
-      <c r="F45" s="29" t="n">
+      <c r="F45" s="25" t="n">
         <v>628</v>
       </c>
     </row>
@@ -1505,16 +1502,16 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="C46" s="29" t="n">
+      <c r="C46" s="25" t="n">
         <v>2142</v>
       </c>
-      <c r="D46" s="29" t="n">
+      <c r="D46" s="25" t="n">
         <v>1725</v>
       </c>
-      <c r="E46" s="29" t="n">
+      <c r="E46" s="25" t="n">
         <v>2726</v>
       </c>
-      <c r="F46" s="29" t="n">
+      <c r="F46" s="25" t="n">
         <v>3132</v>
       </c>
     </row>
@@ -1524,16 +1521,16 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="C47" s="29" t="n">
+      <c r="C47" s="25" t="n">
         <v>66283</v>
       </c>
-      <c r="D47" s="29" t="n">
+      <c r="D47" s="25" t="n">
         <v>64254</v>
       </c>
-      <c r="E47" s="29" t="n">
+      <c r="E47" s="25" t="n">
         <v>69416</v>
       </c>
-      <c r="F47" s="29" t="n">
+      <c r="F47" s="25" t="n">
         <v>82798</v>
       </c>
     </row>
@@ -1543,16 +1540,16 @@
           <t>Total Non Current Assets</t>
         </is>
       </c>
-      <c r="C48" s="29" t="n">
+      <c r="C48" s="25" t="n">
         <v>44502</v>
       </c>
-      <c r="D48" s="29" t="n">
+      <c r="D48" s="25" t="n">
         <v>43010</v>
       </c>
-      <c r="E48" s="29" t="n">
+      <c r="E48" s="25" t="n">
         <v>45044</v>
       </c>
-      <c r="F48" s="29" t="n">
+      <c r="F48" s="25" t="n">
         <v>53957</v>
       </c>
     </row>
@@ -1562,16 +1559,16 @@
           <t>Other Non Current Assets</t>
         </is>
       </c>
-      <c r="C49" s="29" t="n">
+      <c r="C49" s="25" t="n">
         <v>1277</v>
       </c>
-      <c r="D49" s="29" t="n">
+      <c r="D49" s="25" t="n">
         <v>1262</v>
       </c>
-      <c r="E49" s="29" t="n">
+      <c r="E49" s="25" t="n">
         <v>1518</v>
       </c>
-      <c r="F49" s="29" t="n">
+      <c r="F49" s="25" t="n">
         <v>2783</v>
       </c>
     </row>
@@ -1581,16 +1578,16 @@
           <t>Non Current Deferred Assets</t>
         </is>
       </c>
-      <c r="C50" s="29" t="n">
+      <c r="C50" s="25" t="n">
         <v>702</v>
       </c>
-      <c r="D50" s="29" t="n">
+      <c r="D50" s="25" t="n">
         <v>756</v>
       </c>
-      <c r="E50" s="29" t="n">
+      <c r="E50" s="25" t="n">
         <v>520</v>
       </c>
-      <c r="F50" s="29" t="n">
+      <c r="F50" s="25" t="n">
         <v>616</v>
       </c>
     </row>
@@ -1600,16 +1597,16 @@
           <t>Non Current Deferred Taxes Assets</t>
         </is>
       </c>
-      <c r="C51" s="29" t="n">
+      <c r="C51" s="25" t="n">
         <v>702</v>
       </c>
-      <c r="D51" s="29" t="n">
+      <c r="D51" s="25" t="n">
         <v>756</v>
       </c>
-      <c r="E51" s="29" t="n">
+      <c r="E51" s="25" t="n">
         <v>520</v>
       </c>
-      <c r="F51" s="29" t="n">
+      <c r="F51" s="25" t="n">
         <v>616</v>
       </c>
     </row>
@@ -1619,16 +1616,16 @@
           <t>Investments And Advances</t>
         </is>
       </c>
-      <c r="C52" s="29" t="n">
+      <c r="C52" s="25" t="n">
         <v>1647</v>
       </c>
-      <c r="D52" s="29" t="n">
+      <c r="D52" s="25" t="n">
         <v>844</v>
       </c>
-      <c r="E52" s="29" t="n">
+      <c r="E52" s="25" t="n">
         <v>1046</v>
       </c>
-      <c r="F52" s="29" t="n">
+      <c r="F52" s="25" t="n">
         <v>1629</v>
       </c>
     </row>
@@ -1638,16 +1635,16 @@
           <t>Investmentin Financial Assets</t>
         </is>
       </c>
-      <c r="C53" s="29" t="n">
+      <c r="C53" s="25" t="n">
         <v>1647</v>
       </c>
-      <c r="D53" s="29" t="n">
+      <c r="D53" s="25" t="n">
         <v>844</v>
       </c>
-      <c r="E53" s="29" t="n">
+      <c r="E53" s="25" t="n">
         <v>1046</v>
       </c>
-      <c r="F53" s="29" t="n">
+      <c r="F53" s="25" t="n">
         <v>1629</v>
       </c>
     </row>
@@ -1657,16 +1654,16 @@
           <t>Available For Sale Securities</t>
         </is>
       </c>
-      <c r="C54" s="29" t="n">
+      <c r="C54" s="25" t="n">
         <v>1647</v>
       </c>
-      <c r="D54" s="29" t="n">
+      <c r="D54" s="25" t="n">
         <v>844</v>
       </c>
-      <c r="E54" s="29" t="n">
+      <c r="E54" s="25" t="n">
         <v>1046</v>
       </c>
-      <c r="F54" s="29" t="n">
+      <c r="F54" s="25" t="n">
         <v>1629</v>
       </c>
     </row>
@@ -1676,16 +1673,16 @@
           <t>Goodwill And Other Intangible Assets</t>
         </is>
       </c>
-      <c r="C55" s="29" t="n">
+      <c r="C55" s="25" t="n">
         <v>1649</v>
       </c>
-      <c r="D55" s="29" t="n">
+      <c r="D55" s="25" t="n">
         <v>1554</v>
       </c>
-      <c r="E55" s="29" t="n">
+      <c r="E55" s="25" t="n">
         <v>1566</v>
       </c>
-      <c r="F55" s="29" t="n">
+      <c r="F55" s="25" t="n">
         <v>1603</v>
       </c>
     </row>
@@ -1695,16 +1692,16 @@
           <t>Other Intangible Assets</t>
         </is>
       </c>
-      <c r="C56" s="29" t="n">
+      <c r="C56" s="25" t="n">
         <v>421</v>
       </c>
-      <c r="D56" s="29" t="n">
+      <c r="D56" s="25" t="n">
         <v>404</v>
       </c>
-      <c r="E56" s="29" t="n">
+      <c r="E56" s="25" t="n">
         <v>416</v>
       </c>
-      <c r="F56" s="29" t="n">
+      <c r="F56" s="25" t="n">
         <v>453</v>
       </c>
     </row>
@@ -1714,16 +1711,16 @@
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="C57" s="29" t="n">
+      <c r="C57" s="25" t="n">
         <v>1228</v>
       </c>
-      <c r="D57" s="29" t="n">
+      <c r="D57" s="25" t="n">
         <v>1150</v>
       </c>
-      <c r="E57" s="29" t="n">
+      <c r="E57" s="25" t="n">
         <v>1150</v>
       </c>
-      <c r="F57" s="29" t="n">
+      <c r="F57" s="25" t="n">
         <v>1150</v>
       </c>
     </row>
@@ -1733,16 +1730,16 @@
           <t>Net PPE</t>
         </is>
       </c>
-      <c r="C58" s="29" t="n">
+      <c r="C58" s="25" t="n">
         <v>39227</v>
       </c>
-      <c r="D58" s="29" t="n">
+      <c r="D58" s="25" t="n">
         <v>38594</v>
       </c>
-      <c r="E58" s="29" t="n">
+      <c r="E58" s="25" t="n">
         <v>40394</v>
       </c>
-      <c r="F58" s="29" t="n">
+      <c r="F58" s="25" t="n">
         <v>47326</v>
       </c>
     </row>
@@ -1752,16 +1749,16 @@
           <t>Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="C59" s="29" t="n">
+      <c r="C59" s="25" t="n">
         <v>-42782</v>
       </c>
-      <c r="D59" s="29" t="n">
+      <c r="D59" s="25" t="n">
         <v>-49657</v>
       </c>
-      <c r="E59" s="29" t="n">
+      <c r="E59" s="25" t="n">
         <v>-56298</v>
       </c>
-      <c r="F59" s="29" t="n">
+      <c r="F59" s="25" t="n">
         <v>-63106</v>
       </c>
     </row>
@@ -1771,16 +1768,16 @@
           <t>Gross PPE</t>
         </is>
       </c>
-      <c r="C60" s="29" t="n">
+      <c r="C60" s="25" t="n">
         <v>82009</v>
       </c>
-      <c r="D60" s="29" t="n">
+      <c r="D60" s="25" t="n">
         <v>88251</v>
       </c>
-      <c r="E60" s="29" t="n">
+      <c r="E60" s="25" t="n">
         <v>96692</v>
       </c>
-      <c r="F60" s="29" t="n">
+      <c r="F60" s="25" t="n">
         <v>110432</v>
       </c>
     </row>
@@ -1790,16 +1787,16 @@
           <t>Construction In Progress</t>
         </is>
       </c>
-      <c r="C61" s="29" t="n">
+      <c r="C61" s="25" t="n">
         <v>1897</v>
       </c>
-      <c r="D61" s="29" t="n">
+      <c r="D61" s="25" t="n">
         <v>2464</v>
       </c>
-      <c r="E61" s="29" t="n">
+      <c r="E61" s="25" t="n">
         <v>3444</v>
       </c>
-      <c r="F61" s="29" t="n">
+      <c r="F61" s="25" t="n">
         <v>5518</v>
       </c>
     </row>
@@ -1809,16 +1806,16 @@
           <t>Other Properties</t>
         </is>
       </c>
-      <c r="C62" s="29" t="n">
+      <c r="C62" s="25" t="n">
         <v>62032</v>
       </c>
-      <c r="D62" s="29" t="n">
+      <c r="D62" s="25" t="n">
         <v>66221</v>
       </c>
-      <c r="E62" s="29" t="n">
+      <c r="E62" s="25" t="n">
         <v>71458</v>
       </c>
-      <c r="F62" s="29" t="n">
+      <c r="F62" s="25" t="n">
         <v>80670</v>
       </c>
     </row>
@@ -1828,16 +1825,16 @@
           <t>Machinery Furniture Equipment</t>
         </is>
       </c>
-      <c r="C63" s="29" t="n">
+      <c r="C63" s="25" t="n">
         <v>1124</v>
       </c>
-      <c r="D63" s="29" t="n">
+      <c r="D63" s="25" t="n">
         <v>1316</v>
       </c>
-      <c r="E63" s="29" t="n">
+      <c r="E63" s="25" t="n">
         <v>1365</v>
       </c>
-      <c r="F63" s="29" t="n">
+      <c r="F63" s="25" t="n">
         <v>1651</v>
       </c>
     </row>
@@ -1847,16 +1844,16 @@
           <t>Buildings And Improvements</t>
         </is>
       </c>
-      <c r="C64" s="29" t="n">
+      <c r="C64" s="25" t="n">
         <v>16676</v>
       </c>
-      <c r="D64" s="29" t="n">
+      <c r="D64" s="25" t="n">
         <v>17967</v>
       </c>
-      <c r="E64" s="29" t="n">
+      <c r="E64" s="25" t="n">
         <v>20141</v>
       </c>
-      <c r="F64" s="29" t="n">
+      <c r="F64" s="25" t="n">
         <v>22173</v>
       </c>
     </row>
@@ -1866,16 +1863,16 @@
           <t>Land And Improvements</t>
         </is>
       </c>
-      <c r="C65" s="29" t="n">
+      <c r="C65" s="25" t="n">
         <v>280</v>
       </c>
-      <c r="D65" s="29" t="n">
+      <c r="D65" s="25" t="n">
         <v>283</v>
       </c>
-      <c r="E65" s="29" t="n">
+      <c r="E65" s="25" t="n">
         <v>284</v>
       </c>
-      <c r="F65" s="29" t="n">
+      <c r="F65" s="25" t="n">
         <v>420</v>
       </c>
     </row>
@@ -1885,16 +1882,16 @@
           <t>Properties</t>
         </is>
       </c>
-      <c r="C66" s="29" t="n">
+      <c r="C66" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D66" s="29" t="n">
+      <c r="D66" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E66" s="29" t="n">
+      <c r="E66" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F66" s="29" t="n">
+      <c r="F66" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1904,16 +1901,16 @@
           <t>Current Assets</t>
         </is>
       </c>
-      <c r="C67" s="29" t="n">
+      <c r="C67" s="25" t="n">
         <v>21781</v>
       </c>
-      <c r="D67" s="29" t="n">
+      <c r="D67" s="25" t="n">
         <v>21244</v>
       </c>
-      <c r="E67" s="29" t="n">
+      <c r="E67" s="25" t="n">
         <v>24372</v>
       </c>
-      <c r="F67" s="29" t="n">
+      <c r="F67" s="25" t="n">
         <v>28841</v>
       </c>
     </row>
@@ -1923,16 +1920,16 @@
           <t>Other Current Assets</t>
         </is>
       </c>
-      <c r="C68" s="29" t="n">
+      <c r="C68" s="25" t="n">
         <v>657</v>
       </c>
-      <c r="D68" s="29" t="n">
+      <c r="D68" s="25" t="n">
         <v>820</v>
       </c>
-      <c r="E68" s="29" t="n">
+      <c r="E68" s="25" t="n">
         <v>776</v>
       </c>
-      <c r="F68" s="29" t="n">
+      <c r="F68" s="25" t="n">
         <v>914</v>
       </c>
     </row>
@@ -1942,10 +1939,10 @@
           <t>Assets Held For Sale Current</t>
         </is>
       </c>
-      <c r="B69" s="29" t="n">
+      <c r="B69" s="25" t="n">
         <v>974</v>
       </c>
-      <c r="C69" s="29" t="n">
+      <c r="C69" s="25" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1955,16 +1952,16 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C70" s="29" t="n">
+      <c r="C70" s="25" t="n">
         <v>6663</v>
       </c>
-      <c r="D70" s="29" t="n">
+      <c r="D70" s="25" t="n">
         <v>8387</v>
       </c>
-      <c r="E70" s="29" t="n">
+      <c r="E70" s="25" t="n">
         <v>8875</v>
       </c>
-      <c r="F70" s="29" t="n">
+      <c r="F70" s="25" t="n">
         <v>8355</v>
       </c>
     </row>
@@ -1974,16 +1971,16 @@
           <t>Finished Goods</t>
         </is>
       </c>
-      <c r="C71" s="29" t="n">
+      <c r="C71" s="25" t="n">
         <v>1028</v>
       </c>
-      <c r="D71" s="29" t="n">
+      <c r="D71" s="25" t="n">
         <v>1616</v>
       </c>
-      <c r="E71" s="29" t="n">
+      <c r="E71" s="25" t="n">
         <v>1308</v>
       </c>
-      <c r="F71" s="29" t="n">
+      <c r="F71" s="25" t="n">
         <v>1094</v>
       </c>
     </row>
@@ -1993,16 +1990,16 @@
           <t>Work In Process</t>
         </is>
       </c>
-      <c r="C72" s="29" t="n">
+      <c r="C72" s="25" t="n">
         <v>4830</v>
       </c>
-      <c r="D72" s="29" t="n">
+      <c r="D72" s="25" t="n">
         <v>6111</v>
       </c>
-      <c r="E72" s="29" t="n">
+      <c r="E72" s="25" t="n">
         <v>6774</v>
       </c>
-      <c r="F72" s="29" t="n">
+      <c r="F72" s="25" t="n">
         <v>6401</v>
       </c>
     </row>
@@ -2012,16 +2009,16 @@
           <t>Raw Materials</t>
         </is>
       </c>
-      <c r="C73" s="29" t="n">
+      <c r="C73" s="25" t="n">
         <v>805</v>
       </c>
-      <c r="D73" s="29" t="n">
+      <c r="D73" s="25" t="n">
         <v>660</v>
       </c>
-      <c r="E73" s="29" t="n">
+      <c r="E73" s="25" t="n">
         <v>793</v>
       </c>
-      <c r="F73" s="29" t="n">
+      <c r="F73" s="25" t="n">
         <v>860</v>
       </c>
     </row>
@@ -2031,16 +2028,16 @@
           <t>Receivables</t>
         </is>
       </c>
-      <c r="C74" s="29" t="n">
+      <c r="C74" s="25" t="n">
         <v>5130</v>
       </c>
-      <c r="D74" s="29" t="n">
+      <c r="D74" s="25" t="n">
         <v>2443</v>
       </c>
-      <c r="E74" s="29" t="n">
+      <c r="E74" s="25" t="n">
         <v>6615</v>
       </c>
-      <c r="F74" s="29" t="n">
+      <c r="F74" s="25" t="n">
         <v>9265</v>
       </c>
     </row>
@@ -2050,16 +2047,16 @@
           <t>Other Receivables</t>
         </is>
       </c>
-      <c r="C75" s="29" t="n">
+      <c r="C75" s="25" t="n">
         <v>114</v>
       </c>
-      <c r="D75" s="29" t="n">
+      <c r="D75" s="25" t="n">
         <v>201</v>
       </c>
-      <c r="E75" s="29" t="n">
+      <c r="E75" s="25" t="n">
         <v>928</v>
       </c>
-      <c r="F75" s="29" t="n">
+      <c r="F75" s="25" t="n">
         <v>1666</v>
       </c>
     </row>
@@ -2069,16 +2066,16 @@
           <t>Taxes Receivable</t>
         </is>
       </c>
-      <c r="C76" s="29" t="n">
+      <c r="C76" s="25" t="n">
         <v>251</v>
       </c>
-      <c r="D76" s="29" t="n">
+      <c r="D76" s="25" t="n">
         <v>194</v>
       </c>
-      <c r="E76" s="29" t="n">
+      <c r="E76" s="25" t="n">
         <v>268</v>
       </c>
-      <c r="F76" s="29" t="n">
+      <c r="F76" s="25" t="n">
         <v>436</v>
       </c>
     </row>
@@ -2088,16 +2085,16 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="C77" s="29" t="n">
+      <c r="C77" s="25" t="n">
         <v>4765</v>
       </c>
-      <c r="D77" s="29" t="n">
+      <c r="D77" s="25" t="n">
         <v>2048</v>
       </c>
-      <c r="E77" s="29" t="n">
+      <c r="E77" s="25" t="n">
         <v>5419</v>
       </c>
-      <c r="F77" s="29" t="n">
+      <c r="F77" s="25" t="n">
         <v>7163</v>
       </c>
     </row>
@@ -2107,16 +2104,16 @@
           <t>Cash Cash Equivalents And Short Term Investments</t>
         </is>
       </c>
-      <c r="C78" s="29" t="n">
+      <c r="C78" s="25" t="n">
         <v>9331</v>
       </c>
-      <c r="D78" s="29" t="n">
+      <c r="D78" s="25" t="n">
         <v>9594</v>
       </c>
-      <c r="E78" s="29" t="n">
+      <c r="E78" s="25" t="n">
         <v>8106</v>
       </c>
-      <c r="F78" s="29" t="n">
+      <c r="F78" s="25" t="n">
         <v>10307</v>
       </c>
     </row>
@@ -2126,16 +2123,16 @@
           <t>Other Short Term Investments</t>
         </is>
       </c>
-      <c r="C79" s="29" t="n">
+      <c r="C79" s="25" t="n">
         <v>1069</v>
       </c>
-      <c r="D79" s="29" t="n">
+      <c r="D79" s="25" t="n">
         <v>1017</v>
       </c>
-      <c r="E79" s="29" t="n">
+      <c r="E79" s="25" t="n">
         <v>1065</v>
       </c>
-      <c r="F79" s="29" t="n">
+      <c r="F79" s="25" t="n">
         <v>665</v>
       </c>
     </row>
@@ -2145,16 +2142,16 @@
           <t>Cash And Cash Equivalents</t>
         </is>
       </c>
-      <c r="C80" s="29" t="n">
+      <c r="C80" s="25" t="n">
         <v>8262</v>
       </c>
-      <c r="D80" s="29" t="n">
+      <c r="D80" s="25" t="n">
         <v>8577</v>
       </c>
-      <c r="E80" s="29" t="n">
+      <c r="E80" s="25" t="n">
         <v>7041</v>
       </c>
-      <c r="F80" s="29" t="n">
+      <c r="F80" s="25" t="n">
         <v>9642</v>
       </c>
     </row>
@@ -2164,16 +2161,16 @@
           <t>Cash Equivalents</t>
         </is>
       </c>
-      <c r="C81" s="29" t="n">
+      <c r="C81" s="25" t="n">
         <v>2207</v>
       </c>
-      <c r="D81" s="29" t="n">
+      <c r="D81" s="25" t="n">
         <v>2806</v>
       </c>
-      <c r="E81" s="29" t="n">
+      <c r="E81" s="25" t="n">
         <v>387</v>
       </c>
-      <c r="F81" s="29" t="n">
+      <c r="F81" s="25" t="n">
         <v>1767</v>
       </c>
     </row>
@@ -2183,16 +2180,16 @@
           <t>Cash Financial</t>
         </is>
       </c>
-      <c r="C82" s="29" t="n">
+      <c r="C82" s="25" t="n">
         <v>6055</v>
       </c>
-      <c r="D82" s="29" t="n">
+      <c r="D82" s="25" t="n">
         <v>5771</v>
       </c>
-      <c r="E82" s="29" t="n">
+      <c r="E82" s="25" t="n">
         <v>6654</v>
       </c>
-      <c r="F82" s="29" t="n">
+      <c r="F82" s="25" t="n">
         <v>7875</v>
       </c>
     </row>
@@ -2228,7 +2225,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As reported by yfinance (USDmm). Hardcoded actuals.</t>
+          <t>As reported by Yahoo snapshot as of 2026-07-09 (USDmm). Hardcoded actuals.</t>
         </is>
       </c>
     </row>
@@ -2270,16 +2267,16 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="25" t="n">
         <v>3114</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>-6117</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="25" t="n">
         <v>121</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="25" t="n">
         <v>1668</v>
       </c>
     </row>
@@ -2289,16 +2286,16 @@
           <t>Repurchase Of Capital Stock</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="25" t="n">
         <v>-2432</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="25" t="n">
         <v>-425</v>
       </c>
-      <c r="E6" s="29" t="n">
+      <c r="E6" s="25" t="n">
         <v>-300</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2308,16 +2305,16 @@
           <t>Repayment Of Debt</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="25" t="n">
         <v>-2032</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="25" t="n">
         <v>-761</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="25" t="n">
         <v>-1897</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="25" t="n">
         <v>-4619</v>
       </c>
     </row>
@@ -2327,16 +2324,16 @@
           <t>Issuance Of Debt</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="25" t="n">
         <v>2000</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="25" t="n">
         <v>6716</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="25" t="n">
         <v>999</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="25" t="n">
         <v>4430</v>
       </c>
     </row>
@@ -2346,16 +2343,16 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>-12067</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>-7676</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="25" t="n">
         <v>-8386</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="25" t="n">
         <v>-15857</v>
       </c>
     </row>
@@ -2365,16 +2362,16 @@
           <t>Interest Paid Supplemental Data</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="25" t="n">
         <v>154</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="25" t="n">
         <v>323</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="25" t="n">
         <v>503</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="25" t="n">
         <v>418</v>
       </c>
     </row>
@@ -2384,16 +2381,16 @@
           <t>Income Tax Paid Supplemental Data</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="25" t="n">
         <v>493</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="25" t="n">
         <v>532</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="25" t="n">
         <v>338</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="25" t="n">
         <v>583</v>
       </c>
     </row>
@@ -2403,16 +2400,16 @@
           <t>End Cash Position</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>8339</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>8656</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="25" t="n">
         <v>7052</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="25" t="n">
         <v>9646</v>
       </c>
     </row>
@@ -2422,16 +2419,16 @@
           <t>Beginning Cash Position</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>7829</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>8339</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="25" t="n">
         <v>8656</v>
       </c>
-      <c r="F13" s="29" t="n">
+      <c r="F13" s="25" t="n">
         <v>7052</v>
       </c>
     </row>
@@ -2441,16 +2438,16 @@
           <t>Effect Of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="25" t="n">
         <v>-106</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="25" t="n">
         <v>-34</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="25" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2460,16 +2457,16 @@
           <t>Changes In Cash</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="25" t="n">
         <v>616</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="25" t="n">
         <v>351</v>
       </c>
-      <c r="E15" s="29" t="n">
+      <c r="E15" s="25" t="n">
         <v>-1644</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="25" t="n">
         <v>2588</v>
       </c>
     </row>
@@ -2479,16 +2476,16 @@
           <t>Financing Cash Flow</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="25" t="n">
         <v>-2980</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="25" t="n">
         <v>4983</v>
       </c>
-      <c r="E16" s="29" t="n">
+      <c r="E16" s="25" t="n">
         <v>-1842</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="25" t="n">
         <v>-850</v>
       </c>
     </row>
@@ -2498,16 +2495,16 @@
           <t>Cash Flow From Continuing Financing Activities</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="25" t="n">
         <v>-2980</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="25" t="n">
         <v>4983</v>
       </c>
-      <c r="E17" s="29" t="n">
+      <c r="E17" s="25" t="n">
         <v>-1842</v>
       </c>
-      <c r="F17" s="29" t="n">
+      <c r="F17" s="25" t="n">
         <v>-850</v>
       </c>
     </row>
@@ -2517,16 +2514,16 @@
           <t>Net Other Financing Charges</t>
         </is>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="25" t="n">
         <v>-55</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="25" t="n">
         <v>-43</v>
       </c>
-      <c r="E18" s="29" t="n">
+      <c r="E18" s="25" t="n">
         <v>-131</v>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="25" t="n">
         <v>-139</v>
       </c>
     </row>
@@ -2536,10 +2533,10 @@
           <t>Proceeds From Stock Option Exercised</t>
         </is>
       </c>
-      <c r="B19" s="29" t="n">
+      <c r="B19" s="25" t="n">
         <v>-94</v>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="25" t="n">
         <v>-125</v>
       </c>
     </row>
@@ -2549,16 +2546,16 @@
           <t>Cash Dividends Paid</t>
         </is>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="25" t="n">
         <v>-461</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="25" t="n">
         <v>-504</v>
       </c>
-      <c r="E20" s="29" t="n">
+      <c r="E20" s="25" t="n">
         <v>-513</v>
       </c>
-      <c r="F20" s="29" t="n">
+      <c r="F20" s="25" t="n">
         <v>-522</v>
       </c>
     </row>
@@ -2568,16 +2565,16 @@
           <t>Common Stock Dividend Paid</t>
         </is>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="25" t="n">
         <v>-461</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="25" t="n">
         <v>-504</v>
       </c>
-      <c r="E21" s="29" t="n">
+      <c r="E21" s="25" t="n">
         <v>-513</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="25" t="n">
         <v>-522</v>
       </c>
     </row>
@@ -2587,16 +2584,16 @@
           <t>Net Common Stock Issuance</t>
         </is>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="25" t="n">
         <v>-2432</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="25" t="n">
         <v>-425</v>
       </c>
-      <c r="E22" s="29" t="n">
+      <c r="E22" s="25" t="n">
         <v>-300</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2606,16 +2603,16 @@
           <t>Common Stock Payments</t>
         </is>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="25" t="n">
         <v>-2432</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="25" t="n">
         <v>-425</v>
       </c>
-      <c r="E23" s="29" t="n">
+      <c r="E23" s="25" t="n">
         <v>-300</v>
       </c>
-      <c r="F23" s="29" t="n">
+      <c r="F23" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2625,16 +2622,16 @@
           <t>Net Issuance Payments Of Debt</t>
         </is>
       </c>
-      <c r="C24" s="29" t="n">
+      <c r="C24" s="25" t="n">
         <v>-32</v>
       </c>
-      <c r="D24" s="29" t="n">
+      <c r="D24" s="25" t="n">
         <v>5955</v>
       </c>
-      <c r="E24" s="29" t="n">
+      <c r="E24" s="25" t="n">
         <v>-898</v>
       </c>
-      <c r="F24" s="29" t="n">
+      <c r="F24" s="25" t="n">
         <v>-189</v>
       </c>
     </row>
@@ -2644,16 +2641,16 @@
           <t>Net Long Term Debt Issuance</t>
         </is>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="25" t="n">
         <v>-32</v>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="25" t="n">
         <v>5955</v>
       </c>
-      <c r="E25" s="29" t="n">
+      <c r="E25" s="25" t="n">
         <v>-898</v>
       </c>
-      <c r="F25" s="29" t="n">
+      <c r="F25" s="25" t="n">
         <v>-189</v>
       </c>
     </row>
@@ -2663,16 +2660,16 @@
           <t>Long Term Debt Payments</t>
         </is>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="25" t="n">
         <v>-2032</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="25" t="n">
         <v>-761</v>
       </c>
-      <c r="E26" s="29" t="n">
+      <c r="E26" s="25" t="n">
         <v>-1897</v>
       </c>
-      <c r="F26" s="29" t="n">
+      <c r="F26" s="25" t="n">
         <v>-4619</v>
       </c>
     </row>
@@ -2682,16 +2679,16 @@
           <t>Long Term Debt Issuance</t>
         </is>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="25" t="n">
         <v>2000</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="25" t="n">
         <v>6716</v>
       </c>
-      <c r="E27" s="29" t="n">
+      <c r="E27" s="25" t="n">
         <v>999</v>
       </c>
-      <c r="F27" s="29" t="n">
+      <c r="F27" s="25" t="n">
         <v>4430</v>
       </c>
     </row>
@@ -2701,16 +2698,16 @@
           <t>Investing Cash Flow</t>
         </is>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="25" t="n">
         <v>-11585</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="25" t="n">
         <v>-6191</v>
       </c>
-      <c r="E28" s="29" t="n">
+      <c r="E28" s="25" t="n">
         <v>-8309</v>
       </c>
-      <c r="F28" s="29" t="n">
+      <c r="F28" s="25" t="n">
         <v>-14087</v>
       </c>
     </row>
@@ -2720,16 +2717,16 @@
           <t>Cash Flow From Continuing Investing Activities</t>
         </is>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="25" t="n">
         <v>-11585</v>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="25" t="n">
         <v>-6191</v>
       </c>
-      <c r="E29" s="29" t="n">
+      <c r="E29" s="25" t="n">
         <v>-8309</v>
       </c>
-      <c r="F29" s="29" t="n">
+      <c r="F29" s="25" t="n">
         <v>-14087</v>
       </c>
     </row>
@@ -2739,16 +2736,16 @@
           <t>Net Other Investing Changes</t>
         </is>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="25" t="n">
         <v>-251</v>
       </c>
-      <c r="D30" s="29" t="n">
+      <c r="D30" s="25" t="n">
         <v>617</v>
       </c>
-      <c r="E30" s="29" t="n">
+      <c r="E30" s="25" t="n">
         <v>282</v>
       </c>
-      <c r="F30" s="29" t="n">
+      <c r="F30" s="25" t="n">
         <v>1962</v>
       </c>
     </row>
@@ -2758,16 +2755,16 @@
           <t>Net Investment Purchase And Sale</t>
         </is>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="25" t="n">
         <v>-155</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="25" t="n">
         <v>868</v>
       </c>
-      <c r="E31" s="29" t="n">
+      <c r="E31" s="25" t="n">
         <v>-205</v>
       </c>
-      <c r="F31" s="29" t="n">
+      <c r="F31" s="25" t="n">
         <v>-192</v>
       </c>
     </row>
@@ -2777,16 +2774,16 @@
           <t>Sale Of Investment</t>
         </is>
       </c>
-      <c r="C32" s="29" t="n">
+      <c r="C32" s="25" t="n">
         <v>1615</v>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D32" s="25" t="n">
         <v>1591</v>
       </c>
-      <c r="E32" s="29" t="n">
+      <c r="E32" s="25" t="n">
         <v>1794</v>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F32" s="25" t="n">
         <v>1698</v>
       </c>
     </row>
@@ -2796,16 +2793,16 @@
           <t>Purchase Of Investment</t>
         </is>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="25" t="n">
         <v>-1770</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="25" t="n">
         <v>-723</v>
       </c>
-      <c r="E33" s="29" t="n">
+      <c r="E33" s="25" t="n">
         <v>-1999</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="25" t="n">
         <v>-1890</v>
       </c>
     </row>
@@ -2815,16 +2812,16 @@
           <t>Net Business Purchase And Sale</t>
         </is>
       </c>
-      <c r="B34" s="29" t="n">
+      <c r="B34" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="25" t="n">
         <v>888</v>
       </c>
-      <c r="D34" s="29" t="n">
+      <c r="D34" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E34" s="29" t="n">
+      <c r="E34" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2834,16 +2831,16 @@
           <t>Sale Of Business</t>
         </is>
       </c>
-      <c r="B35" s="29" t="n">
+      <c r="B35" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="25" t="n">
         <v>888</v>
       </c>
-      <c r="D35" s="29" t="n">
+      <c r="D35" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="29" t="n">
+      <c r="E35" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2853,16 +2850,16 @@
           <t>Capital Expenditure Reported</t>
         </is>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="25" t="n">
         <v>-12067</v>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D36" s="25" t="n">
         <v>-7676</v>
       </c>
-      <c r="E36" s="29" t="n">
+      <c r="E36" s="25" t="n">
         <v>-8386</v>
       </c>
-      <c r="F36" s="29" t="n">
+      <c r="F36" s="25" t="n">
         <v>-15857</v>
       </c>
     </row>
@@ -2872,16 +2869,16 @@
           <t>Operating Cash Flow</t>
         </is>
       </c>
-      <c r="C37" s="29" t="n">
+      <c r="C37" s="25" t="n">
         <v>15181</v>
       </c>
-      <c r="D37" s="29" t="n">
+      <c r="D37" s="25" t="n">
         <v>1559</v>
       </c>
-      <c r="E37" s="29" t="n">
+      <c r="E37" s="25" t="n">
         <v>8507</v>
       </c>
-      <c r="F37" s="29" t="n">
+      <c r="F37" s="25" t="n">
         <v>17525</v>
       </c>
     </row>
@@ -2891,16 +2888,16 @@
           <t>Cash Flow From Continuing Operating Activities</t>
         </is>
       </c>
-      <c r="C38" s="29" t="n">
+      <c r="C38" s="25" t="n">
         <v>15181</v>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D38" s="25" t="n">
         <v>1559</v>
       </c>
-      <c r="E38" s="29" t="n">
+      <c r="E38" s="25" t="n">
         <v>8507</v>
       </c>
-      <c r="F38" s="29" t="n">
+      <c r="F38" s="25" t="n">
         <v>17525</v>
       </c>
     </row>
@@ -2910,16 +2907,16 @@
           <t>Change In Working Capital</t>
         </is>
       </c>
-      <c r="C39" s="29" t="n">
+      <c r="C39" s="25" t="n">
         <v>-1255</v>
       </c>
-      <c r="D39" s="29" t="n">
+      <c r="D39" s="25" t="n">
         <v>-2911</v>
       </c>
-      <c r="E39" s="29" t="n">
+      <c r="E39" s="25" t="n">
         <v>-1165</v>
       </c>
-      <c r="F39" s="29" t="n">
+      <c r="F39" s="25" t="n">
         <v>-666</v>
       </c>
     </row>
@@ -2929,7 +2926,7 @@
           <t>Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B40" s="29" t="n">
+      <c r="B40" s="25" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -2939,16 +2936,16 @@
           <t>Change In Other Current Liabilities</t>
         </is>
       </c>
-      <c r="C41" s="29" t="n">
+      <c r="C41" s="25" t="n">
         <v>400</v>
       </c>
-      <c r="D41" s="29" t="n">
+      <c r="D41" s="25" t="n">
         <v>-817</v>
       </c>
-      <c r="E41" s="29" t="n">
+      <c r="E41" s="25" t="n">
         <v>989</v>
       </c>
-      <c r="F41" s="29" t="n">
+      <c r="F41" s="25" t="n">
         <v>-272</v>
       </c>
     </row>
@@ -2958,16 +2955,16 @@
           <t>Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="C42" s="29" t="n">
+      <c r="C42" s="25" t="n">
         <v>334</v>
       </c>
-      <c r="D42" s="29" t="n">
+      <c r="D42" s="25" t="n">
         <v>-1302</v>
       </c>
-      <c r="E42" s="29" t="n">
+      <c r="E42" s="25" t="n">
         <v>1915</v>
       </c>
-      <c r="F42" s="29" t="n">
+      <c r="F42" s="25" t="n">
         <v>862</v>
       </c>
     </row>
@@ -2977,16 +2974,16 @@
           <t>Change In Inventory</t>
         </is>
       </c>
-      <c r="C43" s="29" t="n">
+      <c r="C43" s="25" t="n">
         <v>-2179</v>
       </c>
-      <c r="D43" s="29" t="n">
+      <c r="D43" s="25" t="n">
         <v>-3555</v>
       </c>
-      <c r="E43" s="29" t="n">
+      <c r="E43" s="25" t="n">
         <v>-488</v>
       </c>
-      <c r="F43" s="29" t="n">
+      <c r="F43" s="25" t="n">
         <v>520</v>
       </c>
     </row>
@@ -2996,16 +2993,16 @@
           <t>Change In Receivables</t>
         </is>
       </c>
-      <c r="C44" s="29" t="n">
+      <c r="C44" s="25" t="n">
         <v>190</v>
       </c>
-      <c r="D44" s="29" t="n">
+      <c r="D44" s="25" t="n">
         <v>2763</v>
       </c>
-      <c r="E44" s="29" t="n">
+      <c r="E44" s="25" t="n">
         <v>-3581</v>
       </c>
-      <c r="F44" s="29" t="n">
+      <c r="F44" s="25" t="n">
         <v>-1776</v>
       </c>
     </row>
@@ -3015,16 +3012,16 @@
           <t>Other Non Cash Items</t>
         </is>
       </c>
-      <c r="C45" s="29" t="n">
+      <c r="C45" s="25" t="n">
         <v>119</v>
       </c>
-      <c r="D45" s="29" t="n">
+      <c r="D45" s="25" t="n">
         <v>19</v>
       </c>
-      <c r="E45" s="29" t="n">
+      <c r="E45" s="25" t="n">
         <v>281</v>
       </c>
-      <c r="F45" s="29" t="n">
+      <c r="F45" s="25" t="n">
         <v>328</v>
       </c>
     </row>
@@ -3034,16 +3031,16 @@
           <t>Stock Based Compensation</t>
         </is>
       </c>
-      <c r="C46" s="29" t="n">
+      <c r="C46" s="25" t="n">
         <v>514</v>
       </c>
-      <c r="D46" s="29" t="n">
+      <c r="D46" s="25" t="n">
         <v>596</v>
       </c>
-      <c r="E46" s="29" t="n">
+      <c r="E46" s="25" t="n">
         <v>833</v>
       </c>
-      <c r="F46" s="29" t="n">
+      <c r="F46" s="25" t="n">
         <v>972</v>
       </c>
     </row>
@@ -3053,16 +3050,16 @@
           <t>Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="C47" s="29" t="n">
+      <c r="C47" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D47" s="29" t="n">
+      <c r="D47" s="25" t="n">
         <v>1932</v>
       </c>
-      <c r="E47" s="29" t="n">
+      <c r="E47" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F47" s="29" t="n">
+      <c r="F47" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3072,16 +3069,16 @@
           <t>Depreciation Amortization Depletion</t>
         </is>
       </c>
-      <c r="C48" s="29" t="n">
+      <c r="C48" s="25" t="n">
         <v>7116</v>
       </c>
-      <c r="D48" s="29" t="n">
+      <c r="D48" s="25" t="n">
         <v>7756</v>
       </c>
-      <c r="E48" s="29" t="n">
+      <c r="E48" s="25" t="n">
         <v>7780</v>
       </c>
-      <c r="F48" s="29" t="n">
+      <c r="F48" s="25" t="n">
         <v>8352</v>
       </c>
     </row>
@@ -3091,16 +3088,16 @@
           <t>Depreciation And Amortization</t>
         </is>
       </c>
-      <c r="C49" s="29" t="n">
+      <c r="C49" s="25" t="n">
         <v>7116</v>
       </c>
-      <c r="D49" s="29" t="n">
+      <c r="D49" s="25" t="n">
         <v>7756</v>
       </c>
-      <c r="E49" s="29" t="n">
+      <c r="E49" s="25" t="n">
         <v>7780</v>
       </c>
-      <c r="F49" s="29" t="n">
+      <c r="F49" s="25" t="n">
         <v>8352</v>
       </c>
     </row>
@@ -3110,10 +3107,10 @@
           <t>Operating Gains Losses</t>
         </is>
       </c>
-      <c r="B50" s="29" t="n">
+      <c r="B50" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="C50" s="29" t="n">
+      <c r="C50" s="25" t="n">
         <v>83</v>
       </c>
     </row>
@@ -3123,16 +3120,16 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="C51" s="29" t="n">
+      <c r="C51" s="25" t="n">
         <v>8687</v>
       </c>
-      <c r="D51" s="29" t="n">
+      <c r="D51" s="25" t="n">
         <v>-5833</v>
       </c>
-      <c r="E51" s="29" t="n">
+      <c r="E51" s="25" t="n">
         <v>778</v>
       </c>
-      <c r="F51" s="29" t="n">
+      <c r="F51" s="25" t="n">
         <v>8539</v>
       </c>
     </row>
@@ -3142,6 +3139,292 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MU — 12-month price target (lens triangulation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Blue = inputs (weights, Ke, dividends, Street weight); black = live formulas. Change a weight and the blended fair value and target recalculate. Guardrail exclusions are already reflected in the effective weights.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Value / share</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Discounted cash flow (FCFF)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>intrinsic</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>490.5879139380186</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>411.2563747263457</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>582.4683357171762</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>0.2028985507246377</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>ok — down-weighted: 0.4x the median of the other lenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Forward P/E</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1269.66327309009</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1041.123883933874</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1498.202662246306</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>0.4347826086956522</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Forward EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1240.33347405206</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>1016.281182540441</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1464.385765563679</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0.3623188405797102</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Weights sum</t>
+        </is>
+      </c>
+      <c r="B9" s="12">
+        <f>SUM(F5:F7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Blended fair value (today)</t>
+        </is>
+      </c>
+      <c r="B10" s="14">
+        <f>SUMPRODUCT(C5:C7,F5:F7)/SUM(F5:F7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Cost of equity (Ke)</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>0.1138122903126128</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Dividends per share (12m)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>0.4622</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Model 12-month target = FV×(1+Ke)−DPS</t>
+        </is>
+      </c>
+      <c r="B13" s="16">
+        <f>$B$10*(1+$B$11)-$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Street mean target</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Street weight in target</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Published 12-month target</t>
+        </is>
+      </c>
+      <c r="B16" s="17">
+        <f>(1-$B$15)*$B$13+$B$15*$B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Current price</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>948.8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Engine target (incl. plausibility band)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>1264.833590981985</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Guardrails</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Discounted cash flow (FCFF) sits 0.4x the lens median and was down-weighted by 60%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Target anchored 15% to the Street consensus ($1,486.00); model-only target $1,225.80.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3166,14 +3449,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MU — projected P&amp;L &amp; levered FCF (analyst-driven)</t>
+          <t>MU — projected P&amp;L &amp; levered FCF (DCF base case)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Blue = analyst estimates; black = live formulas. The Levered FCF row is the exact cash flow discounted on the 'SWS Valuation' sheet — P&amp;L, cash flow and fair value are one reconciled chain.</t>
+          <t>Blue = consensus-sourced figures; black = live formulas. Revenue and EBIT margin are the DCF base-case drivers; levered FCF = unlevered FCF less after-tax interest.</t>
         </is>
       </c>
     </row>
@@ -3235,40 +3518,40 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Revenue (mn)</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
-        <v>129585.33546</v>
-      </c>
-      <c r="C5" s="12" t="n">
-        <v>234244.72475</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>448303.4103446687</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>801050.9487743712</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>1329644.443596859</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>2038211.967589626</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <v>2865573.160533444</v>
-      </c>
-      <c r="I5" s="13" t="n">
-        <v>3664924.793664249</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>4221901.739181372</v>
-      </c>
-      <c r="K5" s="13" t="n">
-        <v>4327449.282660907</v>
+      <c r="B5" s="18" t="n">
+        <v>129590</v>
+      </c>
+      <c r="C5" s="18" t="n">
+        <v>234240</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>258619.8028564394</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>279149.0796650785</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>296566.539726581</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>311606.8470605715</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>324907.1385926625</v>
+      </c>
+      <c r="I5" s="19" t="n">
+        <v>336980.6129812768</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>348222.8721527889</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>356928.4439566086</v>
       </c>
     </row>
     <row r="6">
@@ -3282,39 +3565,39 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="12">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="12">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="12">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="12">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="12">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="12">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="12">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="12">
         <f>J5/I5-1</f>
         <v/>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="12">
         <f>K5/J5-1</f>
         <v/>
       </c>
@@ -3325,35 +3608,35 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
-        <v>0.2624270961528172</v>
-      </c>
-      <c r="C7" s="15" t="n">
-        <v>0.2624270961528172</v>
-      </c>
-      <c r="D7" s="15" t="n">
-        <v>0.2624270961528172</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>0.2624270961528172</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>0.2624270961528172</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>0.2624270961528172</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>0.2624270961528172</v>
-      </c>
-      <c r="I7" s="15" t="n">
-        <v>0.2624270961528172</v>
-      </c>
-      <c r="J7" s="15" t="n">
-        <v>0.2624270961528172</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>0.2624270961528172</v>
+      <c r="B7" s="11" t="n">
+        <v>0.4734865725989986</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>0.4734865725989986</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>0.4331939645867951</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>0.3929013565745916</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0.3526087485623881</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>0.3123161405501845</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>0.2720235325379809</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>0.2317309245257775</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>0.2317309245257775</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>0.2317309245257775</v>
       </c>
     </row>
     <row r="8">
@@ -3362,43 +3645,43 @@
           <t>EBIT (mn)</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="19">
         <f>B5*B7</f>
         <v/>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="19">
         <f>C5*C7</f>
         <v/>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="19">
         <f>D5*D7</f>
         <v/>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="19">
         <f>E5*E7</f>
         <v/>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="19">
         <f>F5*F7</f>
         <v/>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="19">
         <f>G5*G7</f>
         <v/>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="19">
         <f>H5*H7</f>
         <v/>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="19">
         <f>I5*I7</f>
         <v/>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="19">
         <f>J5*J7</f>
         <v/>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="19">
         <f>K5*K7</f>
         <v/>
       </c>
@@ -3409,35 +3692,35 @@
           <t>Net income (mn)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
-        <v>82812.58338810234</v>
-      </c>
-      <c r="C9" s="13" t="n">
-        <v>52882.26007212917</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>101207.3913825426</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>180842.4272918962</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>300175.8240011362</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>460139.5206113417</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>646921.6555155005</v>
-      </c>
-      <c r="I9" s="13" t="n">
-        <v>827380.4513215494</v>
-      </c>
-      <c r="J9" s="13" t="n">
-        <v>953121.5954111418</v>
-      </c>
-      <c r="K9" s="13" t="n">
-        <v>976949.6352964203</v>
+      <c r="B9" s="18" t="n">
+        <v>82807.10583131999</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>169002.39111564</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>90251.46527010441</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>88346.6223310115</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>84215.6520223738</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>78348.49884989558</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>71117.85032809456</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>62790.08135416255</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>64897.74213834155</v>
+      </c>
+      <c r="K9" s="19" t="n">
+        <v>66529.83334126099</v>
       </c>
     </row>
     <row r="10">
@@ -3488,40 +3771,40 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Levered FCF (mn)</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
-        <v>82812.58338810234</v>
-      </c>
-      <c r="C12" s="17" t="n">
-        <v>169000.6518501875</v>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>326003.8397810436</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>592433.1486843799</v>
-      </c>
-      <c r="F12" s="17" t="n">
-        <v>1010398.895318363</v>
-      </c>
-      <c r="G12" s="17" t="n">
-        <v>1610329.15217504</v>
-      </c>
-      <c r="H12" s="17" t="n">
-        <v>2386515.342321874</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>3270131.027217511</v>
-      </c>
-      <c r="J12" s="17" t="n">
-        <v>4115467.552355631</v>
-      </c>
-      <c r="K12" s="17" t="n">
-        <v>4719417.232331335</v>
+      <c r="B12" s="20" t="n">
+        <v>28805.05181774065</v>
+      </c>
+      <c r="C12" s="20" t="n">
+        <v>59492.03935788296</v>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>67143.9585526841</v>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>65886.41222891305</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>62836.08219156035</v>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>58373.33348664458</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>52795.41335332842</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>46319.25506899595</v>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>50446.45970531934</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>54487.19885313424</v>
       </c>
     </row>
     <row r="13">
@@ -3530,43 +3813,43 @@
           <t>FCF margin</t>
         </is>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="12">
         <f>B12/B5</f>
         <v/>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="12">
         <f>C12/C5</f>
         <v/>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="12">
         <f>D12/D5</f>
         <v/>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="12">
         <f>E12/E5</f>
         <v/>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="12">
         <f>F12/F5</f>
         <v/>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="12">
         <f>G12/G5</f>
         <v/>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="12">
         <f>H12/H5</f>
         <v/>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="12">
         <f>I12/I5</f>
         <v/>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="12">
         <f>J12/J5</f>
         <v/>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="12">
         <f>K12/K5</f>
         <v/>
       </c>
@@ -3574,438 +3857,8 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>→ These Levered FCF figures feed the DCF on the 'SWS Valuation' sheet.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>MU — 2-Stage Free Cash Flow to Equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Simply Wall St methodology. Blue = analyst inputs you can change; black = live formulas. Discounted at the cost of equity. Every figure is traceable; change a blue cell and the model recalculates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Cost of equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Risk-free rate</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="n">
-        <v>0.036</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Equity risk premium</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="n">
-        <v>0.046</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Levered beta (clamped 0.8–2.0)</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="n">
-        <v>1.214</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Cost of equity = Rf + β·ERP</t>
-        </is>
-      </c>
-      <c r="B8" s="20">
-        <f>$B$5+$B$7*$B$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Perpetual growth (g)</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="n">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Shares outstanding (mn)</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="n">
-        <v>1129.393151</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Stage 1 — 10-year cash-flow forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Cash flow (mn)</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Discount factor</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>PV (mn)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="21" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B15" s="12" t="n">
-        <v>82812.58338810234</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D15" s="22">
-        <f>1/(1+$B$8)^1</f>
-        <v/>
-      </c>
-      <c r="E15" s="13">
-        <f>B15*D15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="21" t="n">
-        <v>2027</v>
-      </c>
-      <c r="B16" s="12" t="n">
-        <v>169000.6518501875</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D16" s="22">
-        <f>1/(1+$B$8)^2</f>
-        <v/>
-      </c>
-      <c r="E16" s="13">
-        <f>B16*D16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="n">
-        <v>2028</v>
-      </c>
-      <c r="B17" s="12" t="n">
-        <v>326003.8397810436</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D17" s="22">
-        <f>1/(1+$B$8)^3</f>
-        <v/>
-      </c>
-      <c r="E17" s="13">
-        <f>B17*D17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="21" t="n">
-        <v>2029</v>
-      </c>
-      <c r="B18" s="12" t="n">
-        <v>592433.1486843799</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D18" s="22">
-        <f>1/(1+$B$8)^4</f>
-        <v/>
-      </c>
-      <c r="E18" s="13">
-        <f>B18*D18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="n">
-        <v>2030</v>
-      </c>
-      <c r="B19" s="12" t="n">
-        <v>1010398.895318363</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D19" s="22">
-        <f>1/(1+$B$8)^5</f>
-        <v/>
-      </c>
-      <c r="E19" s="13">
-        <f>B19*D19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="21" t="n">
-        <v>2031</v>
-      </c>
-      <c r="B20" s="12" t="n">
-        <v>1610329.15217504</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D20" s="22">
-        <f>1/(1+$B$8)^6</f>
-        <v/>
-      </c>
-      <c r="E20" s="13">
-        <f>B20*D20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="21" t="n">
-        <v>2032</v>
-      </c>
-      <c r="B21" s="12" t="n">
-        <v>2386515.342321874</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D21" s="22">
-        <f>1/(1+$B$8)^7</f>
-        <v/>
-      </c>
-      <c r="E21" s="13">
-        <f>B21*D21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="21" t="n">
-        <v>2033</v>
-      </c>
-      <c r="B22" s="12" t="n">
-        <v>3270131.027217511</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D22" s="22">
-        <f>1/(1+$B$8)^8</f>
-        <v/>
-      </c>
-      <c r="E22" s="13">
-        <f>B22*D22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="n">
-        <v>2034</v>
-      </c>
-      <c r="B23" s="12" t="n">
-        <v>4115467.552355631</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D23" s="22">
-        <f>1/(1+$B$8)^9</f>
-        <v/>
-      </c>
-      <c r="E23" s="13">
-        <f>B23*D23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="21" t="n">
-        <v>2035</v>
-      </c>
-      <c r="B24" s="12" t="n">
-        <v>4719417.232331335</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D24" s="22">
-        <f>1/(1+$B$8)^10</f>
-        <v/>
-      </c>
-      <c r="E24" s="13">
-        <f>B24*D24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>PV of next 10 years' cash flows</t>
-        </is>
-      </c>
-      <c r="B25" s="23">
-        <f>SUM(E15:E24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Stage 2 — terminal value</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Terminal value = CFn·(1+g)/(Ke−g)</t>
-        </is>
-      </c>
-      <c r="B28" s="13">
-        <f>B24*(1+$B$10)/($B$8-$B$10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>PV of terminal value</t>
-        </is>
-      </c>
-      <c r="B29" s="13">
-        <f>$B$28/(1+$B$8)^10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>Total equity value</t>
-        </is>
-      </c>
-      <c r="B31" s="23">
-        <f>$B$25+$B$29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>Value per share</t>
-        </is>
-      </c>
-      <c r="B32" s="24">
-        <f>$B$31/$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Current price</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>948.8</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Upside / (downside)</t>
-        </is>
-      </c>
-      <c r="B34" s="14">
-        <f>B32/$B$33-1</f>
-        <v/>
+          <t>→ Unlevered FCF (before interest) is what the 'DCF' sheet discounts.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4019,7 +3872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4045,7 +3898,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Blue cells are inputs — change them and the whole model recalculates. Source: yfinance, retrieved 2026-07-09.</t>
+          <t>Blue cells are inputs — change them and the whole model recalculates. Source: Yahoo snapshot as of 2026-07-09, retrieved 2026-10-13.</t>
         </is>
       </c>
     </row>
@@ -4072,7 +3925,7 @@
           <t>Diluted shares (mn)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="18" t="n">
         <v>1129.393151</v>
       </c>
     </row>
@@ -4082,7 +3935,7 @@
           <t>Total debt (USDmm)</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="18" t="n">
         <v>15278</v>
       </c>
     </row>
@@ -4092,7 +3945,7 @@
           <t>Cash &amp; ST investments (USDmm)</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="18" t="n">
         <v>10307</v>
       </c>
     </row>
@@ -4102,7 +3955,7 @@
           <t>Minority interest (USDmm)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4112,7 +3965,7 @@
           <t>Net debt (USDmm)</t>
         </is>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="19">
         <f>Assumptions!$B$7-Assumptions!$B$8</f>
         <v/>
       </c>
@@ -4130,7 +3983,7 @@
           <t>Risk-free rate (Rf)</t>
         </is>
       </c>
-      <c r="B13" s="25" t="n">
+      <c r="B13" s="21" t="n">
         <v>0.043</v>
       </c>
     </row>
@@ -4140,7 +3993,7 @@
           <t>Equity risk premium (ERP)</t>
         </is>
       </c>
-      <c r="B14" s="25" t="n">
+      <c r="B14" s="21" t="n">
         <v>0.046</v>
       </c>
     </row>
@@ -4150,7 +4003,7 @@
           <t>Country risk premium</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4160,7 +4013,7 @@
           <t>Size premium</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4170,8 +4023,8 @@
           <t>Beta (levered)</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n">
-        <v>2.14</v>
+      <c r="B17" s="22" t="n">
+        <v>1.54</v>
       </c>
     </row>
     <row r="18">
@@ -4180,7 +4033,7 @@
           <t>Pre-tax cost of debt</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="15" t="n">
         <v>0.04899999999999999</v>
       </c>
     </row>
@@ -4190,7 +4043,7 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B19" s="15" t="n">
+      <c r="B19" s="11" t="n">
         <v>0.1909727915381248</v>
       </c>
     </row>
@@ -4207,7 +4060,7 @@
           <t>Terminal growth (g)</t>
         </is>
       </c>
-      <c r="B22" s="25" t="n">
+      <c r="B22" s="21" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -4249,6 +4102,31 @@
           <t>FY2030E</t>
         </is>
       </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>FY2031E</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>FY2032E</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>FY2033E</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -4256,19 +4134,34 @@
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="B26" s="15" t="n">
-        <v>0.06713489726936261</v>
-      </c>
-      <c r="C26" s="15" t="n">
-        <v>0.05660117295202196</v>
-      </c>
-      <c r="D26" s="15" t="n">
-        <v>0.0460674486346813</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>0.03553372431734066</v>
-      </c>
-      <c r="F26" s="15" t="n">
+      <c r="B26" s="11" t="n">
+        <v>2.467012681256354</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>0.8075468786171773</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>0.1040804425223677</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>0.07938014251768261</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>0.06239483247589359</v>
+      </c>
+      <c r="G26" s="11" t="n">
+        <v>0.05071478174124758</v>
+      </c>
+      <c r="H26" s="11" t="n">
+        <v>0.04268292451707791</v>
+      </c>
+      <c r="I26" s="11" t="n">
+        <v>0.03715976952956648</v>
+      </c>
+      <c r="J26" s="11" t="n">
+        <v>0.03336173874233148</v>
+      </c>
+      <c r="K26" s="11" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -4278,20 +4171,35 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n">
-        <v>0.2624270961528172</v>
-      </c>
-      <c r="C27" s="15" t="n">
-        <v>0.2432404357852318</v>
-      </c>
-      <c r="D27" s="15" t="n">
-        <v>0.2240537754176464</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>0.204867115050061</v>
-      </c>
-      <c r="F27" s="15" t="n">
-        <v>0.1856804546824756</v>
+      <c r="B27" s="11" t="n">
+        <v>0.4734865725989986</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>0.4734865725989986</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>0.4331939645867951</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>0.3929013565745916</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>0.3526087485623881</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>0.3123161405501845</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>0.2720235325379809</v>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>0.2317309245257775</v>
+      </c>
+      <c r="J27" s="11" t="n">
+        <v>0.2317309245257775</v>
+      </c>
+      <c r="K27" s="11" t="n">
+        <v>0.2317309245257775</v>
       </c>
     </row>
     <row r="28">
@@ -4300,19 +4208,34 @@
           <t>D&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n">
+      <c r="B28" s="11" t="n">
         <v>0.3159312176568507</v>
       </c>
-      <c r="C28" s="15" t="n">
+      <c r="C28" s="11" t="n">
         <v>0.3159312176568507</v>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D28" s="11" t="n">
         <v>0.3159312176568507</v>
       </c>
-      <c r="E28" s="15" t="n">
+      <c r="E28" s="11" t="n">
         <v>0.3159312176568507</v>
       </c>
-      <c r="F28" s="15" t="n">
+      <c r="F28" s="11" t="n">
+        <v>0.3159312176568507</v>
+      </c>
+      <c r="G28" s="11" t="n">
+        <v>0.3159312176568507</v>
+      </c>
+      <c r="H28" s="11" t="n">
+        <v>0.3159312176568507</v>
+      </c>
+      <c r="I28" s="11" t="n">
+        <v>0.3159312176568507</v>
+      </c>
+      <c r="J28" s="11" t="n">
+        <v>0.3159312176568507</v>
+      </c>
+      <c r="K28" s="11" t="n">
         <v>0.3159312176568507</v>
       </c>
     </row>
@@ -4322,20 +4245,35 @@
           <t>Capex % of revenue</t>
         </is>
       </c>
-      <c r="B29" s="15" t="n">
+      <c r="B29" s="11" t="n">
         <v>0.4111156318113486</v>
       </c>
-      <c r="C29" s="15" t="n">
-        <v>0.4111156318113486</v>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>0.4111156318113486</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>0.4111156318113486</v>
-      </c>
-      <c r="F29" s="15" t="n">
-        <v>0.4111156318113486</v>
+      <c r="C29" s="11" t="n">
+        <v>0.404049932657036</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>0.3969842335027235</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>0.389918534348411</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>0.3828528351940985</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>0.375787136039786</v>
+      </c>
+      <c r="H29" s="11" t="n">
+        <v>0.3687214368854734</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>0.3616557377311609</v>
+      </c>
+      <c r="J29" s="11" t="n">
+        <v>0.3545900385768484</v>
+      </c>
+      <c r="K29" s="11" t="n">
+        <v>0.3475243394225359</v>
       </c>
     </row>
     <row r="30">
@@ -4344,7 +4282,7 @@
           <t>ΔNWC % of Δrevenue</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n">
+      <c r="B30" s="11" t="n">
         <v>0.08800693553902628</v>
       </c>
     </row>
@@ -4408,7 +4346,7 @@
           <t>Market value of equity (mm)</t>
         </is>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="23">
         <f>Assumptions!$B$5*Assumptions!$B$6</f>
         <v/>
       </c>
@@ -4419,7 +4357,7 @@
           <t>Debt (book, mm)</t>
         </is>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="23">
         <f>Assumptions!$B$7</f>
         <v/>
       </c>
@@ -4430,7 +4368,7 @@
           <t>Weight of equity</t>
         </is>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="12">
         <f>WACC!$B$6/(WACC!$B$6+WACC!$B$7)</f>
         <v/>
       </c>
@@ -4441,18 +4379,18 @@
           <t>Weight of debt</t>
         </is>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="12">
         <f>1-WACC!$B$8</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="24">
         <f>WACC!$B$8*WACC!$B$4+WACC!$B$9*WACC!$B$5</f>
         <v/>
       </c>
@@ -4468,7 +4406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4481,6 +4419,11 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4548,6 +4491,31 @@
           <t>FY2030E</t>
         </is>
       </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>FY2031E</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>FY2032E</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>FY2033E</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -4555,36 +4523,56 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="25" t="n">
         <v>30758</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="25" t="n">
         <v>15540</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>25111</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="25" t="n">
         <v>37378</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="19">
         <f>E5*(1+Assumptions!B$26)</f>
         <v/>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="19">
         <f>F5*(1+Assumptions!C$26)</f>
         <v/>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="19">
         <f>G5*(1+Assumptions!D$26)</f>
         <v/>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="19">
         <f>H5*(1+Assumptions!E$26)</f>
         <v/>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="19">
         <f>I5*(1+Assumptions!F$26)</f>
+        <v/>
+      </c>
+      <c r="K5" s="19">
+        <f>J5*(1+Assumptions!G$26)</f>
+        <v/>
+      </c>
+      <c r="L5" s="19">
+        <f>K5*(1+Assumptions!H$26)</f>
+        <v/>
+      </c>
+      <c r="M5" s="19">
+        <f>L5*(1+Assumptions!I$26)</f>
+        <v/>
+      </c>
+      <c r="N5" s="19">
+        <f>M5*(1+Assumptions!J$26)</f>
+        <v/>
+      </c>
+      <c r="O5" s="19">
+        <f>N5*(1+Assumptions!K$26)</f>
         <v/>
       </c>
     </row>
@@ -4594,36 +4582,56 @@
           <t xml:space="preserve">  growth %</t>
         </is>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="26">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="26">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="26">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="12">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="12">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="12">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="12">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="12">
         <f>J5/I5-1</f>
+        <v/>
+      </c>
+      <c r="K6" s="12">
+        <f>K5/J5-1</f>
+        <v/>
+      </c>
+      <c r="L6" s="12">
+        <f>L5/K5-1</f>
+        <v/>
+      </c>
+      <c r="M6" s="12">
+        <f>M5/L5-1</f>
+        <v/>
+      </c>
+      <c r="N6" s="12">
+        <f>N5/M5-1</f>
+        <v/>
+      </c>
+      <c r="O6" s="12">
+        <f>O5/N5-1</f>
         <v/>
       </c>
     </row>
@@ -4633,36 +4641,56 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="25" t="n">
         <v>9709</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="25" t="n">
         <v>-5405</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="25" t="n">
         <v>1305</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="25" t="n">
         <v>9809</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="19">
         <f>F5*Assumptions!B$27</f>
         <v/>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="19">
         <f>G5*Assumptions!C$27</f>
         <v/>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="19">
         <f>H5*Assumptions!D$27</f>
         <v/>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="19">
         <f>I5*Assumptions!E$27</f>
         <v/>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="19">
         <f>J5*Assumptions!F$27</f>
+        <v/>
+      </c>
+      <c r="K7" s="19">
+        <f>K5*Assumptions!G$27</f>
+        <v/>
+      </c>
+      <c r="L7" s="19">
+        <f>L5*Assumptions!H$27</f>
+        <v/>
+      </c>
+      <c r="M7" s="19">
+        <f>M5*Assumptions!I$27</f>
+        <v/>
+      </c>
+      <c r="N7" s="19">
+        <f>N5*Assumptions!J$27</f>
+        <v/>
+      </c>
+      <c r="O7" s="19">
+        <f>O5*Assumptions!K$27</f>
         <v/>
       </c>
     </row>
@@ -4672,40 +4700,60 @@
           <t xml:space="preserve">  EBIT margin %</t>
         </is>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="26">
         <f>B7/B5</f>
         <v/>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="26">
         <f>C7/C5</f>
         <v/>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="26">
         <f>D7/D5</f>
         <v/>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="26">
         <f>E7/E5</f>
         <v/>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="12">
         <f>F7/F5</f>
         <v/>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="12">
         <f>G7/G5</f>
         <v/>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="12">
         <f>H7/H5</f>
         <v/>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="12">
         <f>I7/I5</f>
         <v/>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="12">
         <f>J7/J5</f>
+        <v/>
+      </c>
+      <c r="K8" s="12">
+        <f>K7/K5</f>
+        <v/>
+      </c>
+      <c r="L8" s="12">
+        <f>L7/L5</f>
+        <v/>
+      </c>
+      <c r="M8" s="12">
+        <f>M7/M5</f>
+        <v/>
+      </c>
+      <c r="N8" s="12">
+        <f>N7/N5</f>
+        <v/>
+      </c>
+      <c r="O8" s="12">
+        <f>O7/O5</f>
         <v/>
       </c>
     </row>
@@ -4715,36 +4763,56 @@
           <t>D&amp;A</t>
         </is>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="25" t="n">
         <v>7116</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>7756</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>7780</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="25" t="n">
         <v>8352</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="19">
         <f>F5*Assumptions!B$28</f>
         <v/>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="19">
         <f>G5*Assumptions!C$28</f>
         <v/>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="19">
         <f>H5*Assumptions!D$28</f>
         <v/>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="19">
         <f>I5*Assumptions!E$28</f>
         <v/>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="19">
         <f>J5*Assumptions!F$28</f>
+        <v/>
+      </c>
+      <c r="K9" s="19">
+        <f>K5*Assumptions!G$28</f>
+        <v/>
+      </c>
+      <c r="L9" s="19">
+        <f>L5*Assumptions!H$28</f>
+        <v/>
+      </c>
+      <c r="M9" s="19">
+        <f>M5*Assumptions!I$28</f>
+        <v/>
+      </c>
+      <c r="N9" s="19">
+        <f>N5*Assumptions!J$28</f>
+        <v/>
+      </c>
+      <c r="O9" s="19">
+        <f>O5*Assumptions!K$28</f>
         <v/>
       </c>
     </row>
@@ -4754,40 +4822,60 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="27">
         <f>B7+B9</f>
         <v/>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="27">
         <f>C7+C9</f>
         <v/>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="27">
         <f>D7+D9</f>
         <v/>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="27">
         <f>E7+E9</f>
         <v/>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="19">
         <f>F7+F9</f>
         <v/>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="19">
         <f>G7+G9</f>
         <v/>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="19">
         <f>H7+H9</f>
         <v/>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="19">
         <f>I7+I9</f>
         <v/>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="19">
         <f>J7+J9</f>
+        <v/>
+      </c>
+      <c r="K10" s="19">
+        <f>K7+K9</f>
+        <v/>
+      </c>
+      <c r="L10" s="19">
+        <f>L7+L9</f>
+        <v/>
+      </c>
+      <c r="M10" s="19">
+        <f>M7+M9</f>
+        <v/>
+      </c>
+      <c r="N10" s="19">
+        <f>N7+N9</f>
+        <v/>
+      </c>
+      <c r="O10" s="19">
+        <f>O7+O9</f>
         <v/>
       </c>
     </row>
@@ -4797,40 +4885,60 @@
           <t>NOPAT (EBIT×(1−t))</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="28">
         <f>B7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="28">
         <f>C7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="28">
         <f>D7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="28">
         <f>E7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="23">
         <f>F7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="23">
         <f>G7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="23">
         <f>H7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="23">
         <f>I7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="J11" s="27">
+      <c r="J11" s="23">
         <f>J7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="K11" s="23">
+        <f>K7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="L11" s="23">
+        <f>L7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="M11" s="23">
+        <f>M7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="N11" s="23">
+        <f>N7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="O11" s="23">
+        <f>O7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
     </row>
@@ -4840,36 +4948,56 @@
           <t>Capex</t>
         </is>
       </c>
-      <c r="B12" s="29" t="n">
+      <c r="B12" s="25" t="n">
         <v>12067</v>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>7676</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>8386</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="25" t="n">
         <v>15857</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="19">
         <f>F5*Assumptions!B$29</f>
         <v/>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="19">
         <f>G5*Assumptions!C$29</f>
         <v/>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="19">
         <f>H5*Assumptions!D$29</f>
         <v/>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="19">
         <f>I5*Assumptions!E$29</f>
         <v/>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="19">
         <f>J5*Assumptions!F$29</f>
+        <v/>
+      </c>
+      <c r="K12" s="19">
+        <f>K5*Assumptions!G$29</f>
+        <v/>
+      </c>
+      <c r="L12" s="19">
+        <f>L5*Assumptions!H$29</f>
+        <v/>
+      </c>
+      <c r="M12" s="19">
+        <f>M5*Assumptions!I$29</f>
+        <v/>
+      </c>
+      <c r="N12" s="19">
+        <f>N5*Assumptions!J$29</f>
+        <v/>
+      </c>
+      <c r="O12" s="19">
+        <f>O5*Assumptions!K$29</f>
         <v/>
       </c>
     </row>
@@ -4879,79 +5007,119 @@
           <t>Δ Net working capital</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="25" t="n">
         <v>1255</v>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>2911</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>1165</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="25" t="n">
         <v>666</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="19">
         <f>(F5-E5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="19">
         <f>(G5-F5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="19">
         <f>(H5-G5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="19">
         <f>(I5-H5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="19">
         <f>(J5-I5)*Assumptions!$B$30</f>
         <v/>
       </c>
+      <c r="K13" s="19">
+        <f>(K5-J5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="L13" s="19">
+        <f>(L5-K5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="M13" s="19">
+        <f>(M5-L5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="N13" s="19">
+        <f>(N5-M5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="O13" s="19">
+        <f>(O5-N5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>FCFF</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="29">
         <f>B11+B9-B12-B13</f>
         <v/>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="29">
         <f>C11+C9-C12-C13</f>
         <v/>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="29">
         <f>D11+D9-D12-D13</f>
         <v/>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="29">
         <f>E11+E9-E12-E13</f>
         <v/>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="30">
         <f>F11+F9-F12-F13</f>
         <v/>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="30">
         <f>G11+G9-G12-G13</f>
         <v/>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="30">
         <f>H11+H9-H12-H13</f>
         <v/>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="30">
         <f>I11+I9-I12-I13</f>
         <v/>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="30">
         <f>J11+J9-J12-J13</f>
+        <v/>
+      </c>
+      <c r="K14" s="30">
+        <f>K11+K9-K12-K13</f>
+        <v/>
+      </c>
+      <c r="L14" s="30">
+        <f>L11+L9-L12-L13</f>
+        <v/>
+      </c>
+      <c r="M14" s="30">
+        <f>M11+M9-M12-M13</f>
+        <v/>
+      </c>
+      <c r="N14" s="30">
+        <f>N11+N9-N12-N13</f>
+        <v/>
+      </c>
+      <c r="O14" s="30">
+        <f>O11+O9-O12-O13</f>
         <v/>
       </c>
     </row>
@@ -4966,7 +5134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -4976,6 +5144,11 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5023,6 +5196,31 @@
           <t>FY2030E</t>
         </is>
       </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>FY2031E</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>FY2032E</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>FY2033E</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -5030,24 +5228,44 @@
           <t>FCFF (from Model)</t>
         </is>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="23">
         <f>Model!F14</f>
         <v/>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="23">
         <f>Model!G14</f>
         <v/>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="23">
         <f>Model!H14</f>
         <v/>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="23">
         <f>Model!I14</f>
         <v/>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="23">
         <f>Model!J14</f>
+        <v/>
+      </c>
+      <c r="G5" s="23">
+        <f>Model!K14</f>
+        <v/>
+      </c>
+      <c r="H5" s="23">
+        <f>Model!L14</f>
+        <v/>
+      </c>
+      <c r="I5" s="23">
+        <f>Model!M14</f>
+        <v/>
+      </c>
+      <c r="J5" s="23">
+        <f>Model!N14</f>
+        <v/>
+      </c>
+      <c r="K5" s="23">
+        <f>Model!O14</f>
         <v/>
       </c>
     </row>
@@ -5057,20 +5275,35 @@
           <t>Period (mid-year, t−0.5)</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B6" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="C6" s="34" t="n">
+      <c r="C6" s="31" t="n">
         <v>1.5</v>
       </c>
-      <c r="D6" s="34" t="n">
+      <c r="D6" s="31" t="n">
         <v>2.5</v>
       </c>
-      <c r="E6" s="34" t="n">
+      <c r="E6" s="31" t="n">
         <v>3.5</v>
       </c>
-      <c r="F6" s="34" t="n">
+      <c r="F6" s="31" t="n">
         <v>4.5</v>
+      </c>
+      <c r="G6" s="31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H6" s="31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I6" s="31" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J6" s="31" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K6" s="31" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="7">
@@ -5079,24 +5312,44 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B7" s="35">
+      <c r="B7" s="32">
         <f>1/(1+WACC!$B$10)^B6</f>
         <v/>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="32">
         <f>1/(1+WACC!$B$10)^C6</f>
         <v/>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="32">
         <f>1/(1+WACC!$B$10)^D6</f>
         <v/>
       </c>
-      <c r="E7" s="35">
+      <c r="E7" s="32">
         <f>1/(1+WACC!$B$10)^E6</f>
         <v/>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="32">
         <f>1/(1+WACC!$B$10)^F6</f>
+        <v/>
+      </c>
+      <c r="G7" s="32">
+        <f>1/(1+WACC!$B$10)^G6</f>
+        <v/>
+      </c>
+      <c r="H7" s="32">
+        <f>1/(1+WACC!$B$10)^H6</f>
+        <v/>
+      </c>
+      <c r="I7" s="32">
+        <f>1/(1+WACC!$B$10)^I6</f>
+        <v/>
+      </c>
+      <c r="J7" s="32">
+        <f>1/(1+WACC!$B$10)^J6</f>
+        <v/>
+      </c>
+      <c r="K7" s="32">
+        <f>1/(1+WACC!$B$10)^K6</f>
         <v/>
       </c>
     </row>
@@ -5106,24 +5359,44 @@
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="19">
         <f>B5*B7</f>
         <v/>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="19">
         <f>C5*C7</f>
         <v/>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="19">
         <f>D5*D7</f>
         <v/>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="19">
         <f>E5*E7</f>
         <v/>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="19">
         <f>F5*F7</f>
+        <v/>
+      </c>
+      <c r="G8" s="19">
+        <f>G5*G7</f>
+        <v/>
+      </c>
+      <c r="H8" s="19">
+        <f>H5*H7</f>
+        <v/>
+      </c>
+      <c r="I8" s="19">
+        <f>I5*I7</f>
+        <v/>
+      </c>
+      <c r="J8" s="19">
+        <f>J5*J7</f>
+        <v/>
+      </c>
+      <c r="K8" s="19">
+        <f>K5*K7</f>
         <v/>
       </c>
     </row>
@@ -5133,8 +5406,8 @@
           <t>PV of explicit FCFF</t>
         </is>
       </c>
-      <c r="B10" s="13">
-        <f>SUM(B8:F8)</f>
+      <c r="B10" s="19">
+        <f>SUM(B8:K8)</f>
         <v/>
       </c>
     </row>
@@ -5144,8 +5417,8 @@
           <t>Terminal NOPAT (FYn)</t>
         </is>
       </c>
-      <c r="B11" s="27">
-        <f>Model!J11</f>
+      <c r="B11" s="23">
+        <f>Model!O11</f>
         <v/>
       </c>
     </row>
@@ -5155,7 +5428,7 @@
           <t>Invested capital (mm)</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="18" t="n">
         <v>59136</v>
       </c>
     </row>
@@ -5165,8 +5438,8 @@
           <t>Terminal invested capital (scaled w/ revenue)</t>
         </is>
       </c>
-      <c r="B13" s="27">
-        <f>$B$12*Model!J5/Model!E5</f>
+      <c r="B13" s="23">
+        <f>$B$12*Model!O5/Model!E5</f>
         <v/>
       </c>
     </row>
@@ -5176,7 +5449,7 @@
           <t>Terminal ROIC</t>
         </is>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="12">
         <f>MAX($B$11/$B$13,WACC!$B$10)</f>
         <v/>
       </c>
@@ -5187,7 +5460,7 @@
           <t>Terminal reinvestment rate (g/ROIC)</t>
         </is>
       </c>
-      <c r="B15" s="36">
+      <c r="B15" s="33">
         <f>Assumptions!$B$22/$B$14</f>
         <v/>
       </c>
@@ -5198,7 +5471,7 @@
           <t>Terminal value (Gordon)</t>
         </is>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="19">
         <f>$B$11*(1+Assumptions!$B$22)*(1-$B$15)/(WACC!$B$10-Assumptions!$B$22)</f>
         <v/>
       </c>
@@ -5209,8 +5482,8 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="B17" s="13">
-        <f>$B$16/(1+WACC!$B$10)^(5-0.5)</f>
+      <c r="B17" s="19">
+        <f>$B$16/(1+WACC!$B$10)^(10-0.5)</f>
         <v/>
       </c>
     </row>
@@ -5220,18 +5493,18 @@
           <t>TV as % of EV</t>
         </is>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="12">
         <f>$B$17/($B$10+$B$17)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B20" s="23">
+      <c r="B20" s="30">
         <f>$B$10+$B$17</f>
         <v/>
       </c>
@@ -5242,7 +5515,7 @@
           <t>(−) Net debt</t>
         </is>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="23">
         <f>-Assumptions!$B$10</f>
         <v/>
       </c>
@@ -5253,40 +5526,40 @@
           <t>(−) Minority interest</t>
         </is>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="23">
         <f>-Assumptions!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B23" s="23">
+      <c r="B23" s="30">
         <f>$B$20-Assumptions!$B$10-Assumptions!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Value per share</t>
         </is>
       </c>
-      <c r="B24" s="37">
+      <c r="B24" s="34">
         <f>$B$23/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Upside vs price</t>
         </is>
       </c>
-      <c r="B25" s="38">
+      <c r="B25" s="35">
         <f>$B$24/Assumptions!$B$5-1</f>
         <v/>
       </c>
@@ -5328,149 +5601,149 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="11" t="n">
         <v>0.015</v>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="11" t="n">
         <v>0.02</v>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="11" t="n">
         <v>0.025</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="11" t="n">
         <v>0.03</v>
       </c>
-      <c r="F4" s="15" t="n">
+      <c r="F4" s="11" t="n">
         <v>0.035</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
-        <v>0.1250997179150661</v>
+      <c r="A5" s="15" t="n">
+        <v>0.09776966939536565</v>
       </c>
       <c r="B5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$5-B$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$5-B$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$5-C$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$5-C$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$5-D$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$5-D$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$5-E$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$5-E$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$5-F$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$5-F$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
-        <v>0.1325997179150661</v>
+      <c r="A6" s="15" t="n">
+        <v>0.1052696693953656</v>
       </c>
       <c r="B6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$6-B$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$6-B$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$6-C$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$6-C$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$6-D$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$6-D$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$6-E$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$6-E$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$6-F$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$6-F$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
-        <v>0.1400997179150661</v>
+      <c r="A7" s="15" t="n">
+        <v>0.1127696693953656</v>
       </c>
       <c r="B7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$7-B$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$7-B$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$7-C$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$7-C$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$7-D$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$7-D$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$7-E$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$7-E$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$7-F$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$7-F$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
-        <v>0.1475997179150661</v>
+      <c r="A8" s="15" t="n">
+        <v>0.1202696693953657</v>
       </c>
       <c r="B8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$8-B$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$8-B$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$8-C$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$8-C$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$8-D$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$8-D$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$8-E$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$8-E$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$8-F$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$8-F$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
-        <v>0.1550997179150661</v>
+      <c r="A9" s="15" t="n">
+        <v>0.1277696693953657</v>
       </c>
       <c r="B9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$9-B$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$9-B$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$9-C$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$9-C$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$9-D$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$9-D$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$9-E$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$9-E$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$9-F$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$9-F$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -5506,7 +5779,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As reported by yfinance (USDmm). Hardcoded actuals.</t>
+          <t>As reported by Yahoo snapshot as of 2026-07-09 (USDmm). Hardcoded actuals.</t>
         </is>
       </c>
     </row>
@@ -5548,16 +5821,16 @@
           <t>Tax Effect Of Unusual Items</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="25" t="n">
         <v>-5.952</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>-69.3</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="25" t="n">
         <v>-5.46</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="25" t="n">
         <v>-19.72</v>
       </c>
     </row>
@@ -5567,17 +5840,17 @@
           <t>Tax Rate For Calcs</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
-        <v>9.3e-08</v>
-      </c>
-      <c r="D6" s="29" t="n">
-        <v>2.1e-07</v>
-      </c>
-      <c r="E6" s="29" t="n">
-        <v>3.64e-07</v>
-      </c>
-      <c r="F6" s="29" t="n">
-        <v>1.16e-07</v>
+      <c r="C6" s="25" t="n">
+        <v>9.299999999999999e-14</v>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>2.1e-13</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>3.64e-13</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>1.16e-13</v>
       </c>
     </row>
     <row r="7">
@@ -5586,16 +5859,16 @@
           <t>Normalized EBITDA</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="25" t="n">
         <v>16940</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="25" t="n">
         <v>2816</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="25" t="n">
         <v>9597</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="25" t="n">
         <v>18653</v>
       </c>
     </row>
@@ -5605,16 +5878,16 @@
           <t>Total Unusual Items</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="25" t="n">
         <v>-64</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="25" t="n">
         <v>-330</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="25" t="n">
         <v>-15</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="25" t="n">
         <v>-170</v>
       </c>
     </row>
@@ -5624,16 +5897,16 @@
           <t>Total Unusual Items Excluding Goodwill</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>-64</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>-330</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="25" t="n">
         <v>-15</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="25" t="n">
         <v>-170</v>
       </c>
     </row>
@@ -5643,16 +5916,16 @@
           <t>Net Income From Continuing Operation Net Minority Interest</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="25" t="n">
         <v>8687</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="25" t="n">
         <v>-5833</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="25" t="n">
         <v>778</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="25" t="n">
         <v>8539</v>
       </c>
     </row>
@@ -5662,16 +5935,16 @@
           <t>Reconciled Depreciation</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="25" t="n">
         <v>7116</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="25" t="n">
         <v>7756</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="25" t="n">
         <v>7780</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="25" t="n">
         <v>8352</v>
       </c>
     </row>
@@ -5681,16 +5954,16 @@
           <t>Reconciled Cost Of Revenue</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>16860</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>16956</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="25" t="n">
         <v>19498</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="25" t="n">
         <v>22505</v>
       </c>
     </row>
@@ -5700,16 +5973,16 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>16876</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>2486</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="25" t="n">
         <v>9582</v>
       </c>
-      <c r="F13" s="29" t="n">
+      <c r="F13" s="25" t="n">
         <v>18483</v>
       </c>
     </row>
@@ -5719,16 +5992,16 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="25" t="n">
         <v>9760</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="25" t="n">
         <v>-5270</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="25" t="n">
         <v>1802</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="25" t="n">
         <v>10131</v>
       </c>
     </row>
@@ -5738,16 +6011,16 @@
           <t>Net Interest Income</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="25" t="n">
         <v>-93</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="25" t="n">
         <v>80</v>
       </c>
-      <c r="E15" s="29" t="n">
+      <c r="E15" s="25" t="n">
         <v>-33</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="25" t="n">
         <v>19</v>
       </c>
     </row>
@@ -5757,16 +6030,16 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="25" t="n">
         <v>189</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="25" t="n">
         <v>388</v>
       </c>
-      <c r="E16" s="29" t="n">
+      <c r="E16" s="25" t="n">
         <v>562</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="25" t="n">
         <v>477</v>
       </c>
     </row>
@@ -5776,16 +6049,16 @@
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="25" t="n">
         <v>96</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="25" t="n">
         <v>468</v>
       </c>
-      <c r="E17" s="29" t="n">
+      <c r="E17" s="25" t="n">
         <v>529</v>
       </c>
-      <c r="F17" s="29" t="n">
+      <c r="F17" s="25" t="n">
         <v>496</v>
       </c>
     </row>
@@ -5795,16 +6068,16 @@
           <t>Normalized Income</t>
         </is>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="25" t="n">
         <v>8745.048000000001</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="25" t="n">
         <v>-5572.3</v>
       </c>
-      <c r="E18" s="29" t="n">
+      <c r="E18" s="25" t="n">
         <v>787.54</v>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="25" t="n">
         <v>8689.280000000001</v>
       </c>
     </row>
@@ -5814,16 +6087,16 @@
           <t>Net Income From Continuing And Discontinued Operation</t>
         </is>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="25" t="n">
         <v>8687</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="25" t="n">
         <v>-5833</v>
       </c>
-      <c r="E19" s="29" t="n">
+      <c r="E19" s="25" t="n">
         <v>778</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="25" t="n">
         <v>8539</v>
       </c>
     </row>
@@ -5833,16 +6106,16 @@
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="25" t="n">
         <v>21049</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="25" t="n">
         <v>20945</v>
       </c>
-      <c r="E20" s="29" t="n">
+      <c r="E20" s="25" t="n">
         <v>23806</v>
       </c>
-      <c r="F20" s="29" t="n">
+      <c r="F20" s="25" t="n">
         <v>27569</v>
       </c>
     </row>
@@ -5852,16 +6125,16 @@
           <t>Total Operating Income As Reported</t>
         </is>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="25" t="n">
         <v>9702</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="25" t="n">
         <v>-5745</v>
       </c>
-      <c r="E21" s="29" t="n">
+      <c r="E21" s="25" t="n">
         <v>1304</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="25" t="n">
         <v>9770</v>
       </c>
     </row>
@@ -5871,16 +6144,16 @@
           <t>Diluted Average Shares</t>
         </is>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="25" t="n">
         <v>1122</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="25" t="n">
         <v>1093</v>
       </c>
-      <c r="E22" s="29" t="n">
+      <c r="E22" s="25" t="n">
         <v>1118</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="25" t="n">
         <v>1125</v>
       </c>
     </row>
@@ -5890,16 +6163,16 @@
           <t>Basic Average Shares</t>
         </is>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="25" t="n">
         <v>1112</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="25" t="n">
         <v>1093</v>
       </c>
-      <c r="E23" s="29" t="n">
+      <c r="E23" s="25" t="n">
         <v>1105</v>
       </c>
-      <c r="F23" s="29" t="n">
+      <c r="F23" s="25" t="n">
         <v>1116</v>
       </c>
     </row>
@@ -5909,17 +6182,17 @@
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="C24" s="29" t="n">
-        <v>7.75e-06</v>
-      </c>
-      <c r="D24" s="29" t="n">
-        <v>-5.34e-06</v>
-      </c>
-      <c r="E24" s="29" t="n">
-        <v>7e-07</v>
-      </c>
-      <c r="F24" s="29" t="n">
-        <v>7.59e-06</v>
+      <c r="C24" s="25" t="n">
+        <v>7.750000000000001e-12</v>
+      </c>
+      <c r="D24" s="25" t="n">
+        <v>-5.339999999999999e-12</v>
+      </c>
+      <c r="E24" s="25" t="n">
+        <v>6.999999999999999e-13</v>
+      </c>
+      <c r="F24" s="25" t="n">
+        <v>7.59e-12</v>
       </c>
     </row>
     <row r="25">
@@ -5928,17 +6201,17 @@
           <t>Basic EPS</t>
         </is>
       </c>
-      <c r="C25" s="29" t="n">
-        <v>7.81e-06</v>
-      </c>
-      <c r="D25" s="29" t="n">
-        <v>-5.34e-06</v>
-      </c>
-      <c r="E25" s="29" t="n">
-        <v>7e-07</v>
-      </c>
-      <c r="F25" s="29" t="n">
-        <v>7.65e-06</v>
+      <c r="C25" s="25" t="n">
+        <v>7.81e-12</v>
+      </c>
+      <c r="D25" s="25" t="n">
+        <v>-5.339999999999999e-12</v>
+      </c>
+      <c r="E25" s="25" t="n">
+        <v>6.999999999999999e-13</v>
+      </c>
+      <c r="F25" s="25" t="n">
+        <v>7.649999999999999e-12</v>
       </c>
     </row>
     <row r="26">
@@ -5947,16 +6220,16 @@
           <t>Diluted NI Availto Com Stockholders</t>
         </is>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="25" t="n">
         <v>8687</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="25" t="n">
         <v>-5833</v>
       </c>
-      <c r="E26" s="29" t="n">
+      <c r="E26" s="25" t="n">
         <v>778</v>
       </c>
-      <c r="F26" s="29" t="n">
+      <c r="F26" s="25" t="n">
         <v>8539</v>
       </c>
     </row>
@@ -5966,10 +6239,10 @@
           <t>Average Dilution Earnings</t>
         </is>
       </c>
-      <c r="B27" s="29" t="n">
+      <c r="B27" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5979,16 +6252,16 @@
           <t>Net Income Common Stockholders</t>
         </is>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="25" t="n">
         <v>8687</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="25" t="n">
         <v>-5833</v>
       </c>
-      <c r="E28" s="29" t="n">
+      <c r="E28" s="25" t="n">
         <v>778</v>
       </c>
-      <c r="F28" s="29" t="n">
+      <c r="F28" s="25" t="n">
         <v>8539</v>
       </c>
     </row>
@@ -5998,16 +6271,16 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="25" t="n">
         <v>8687</v>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="25" t="n">
         <v>-5833</v>
       </c>
-      <c r="E29" s="29" t="n">
+      <c r="E29" s="25" t="n">
         <v>778</v>
       </c>
-      <c r="F29" s="29" t="n">
+      <c r="F29" s="25" t="n">
         <v>8539</v>
       </c>
     </row>
@@ -6017,10 +6290,10 @@
           <t>Minority Interests</t>
         </is>
       </c>
-      <c r="B30" s="29" t="n">
+      <c r="B30" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6030,16 +6303,16 @@
           <t>Net Income Including Noncontrolling Interests</t>
         </is>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="25" t="n">
         <v>8687</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="25" t="n">
         <v>-5833</v>
       </c>
-      <c r="E31" s="29" t="n">
+      <c r="E31" s="25" t="n">
         <v>778</v>
       </c>
-      <c r="F31" s="29" t="n">
+      <c r="F31" s="25" t="n">
         <v>8539</v>
       </c>
     </row>
@@ -6049,16 +6322,16 @@
           <t>Net Income Continuous Operations</t>
         </is>
       </c>
-      <c r="C32" s="29" t="n">
+      <c r="C32" s="25" t="n">
         <v>8687</v>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D32" s="25" t="n">
         <v>-5833</v>
       </c>
-      <c r="E32" s="29" t="n">
+      <c r="E32" s="25" t="n">
         <v>778</v>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F32" s="25" t="n">
         <v>8539</v>
       </c>
     </row>
@@ -6068,16 +6341,16 @@
           <t>Earnings From Equity Interest Net Of Tax</t>
         </is>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="E33" s="29" t="n">
+      <c r="E33" s="25" t="n">
         <v>-11</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="25" t="n">
         <v>9</v>
       </c>
     </row>
@@ -6087,16 +6360,16 @@
           <t>Tax Provision</t>
         </is>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="25" t="n">
         <v>888</v>
       </c>
-      <c r="D34" s="29" t="n">
+      <c r="D34" s="25" t="n">
         <v>177</v>
       </c>
-      <c r="E34" s="29" t="n">
+      <c r="E34" s="25" t="n">
         <v>451</v>
       </c>
-      <c r="F34" s="29" t="n">
+      <c r="F34" s="25" t="n">
         <v>1124</v>
       </c>
     </row>
@@ -6106,16 +6379,16 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="25" t="n">
         <v>9571</v>
       </c>
-      <c r="D35" s="29" t="n">
+      <c r="D35" s="25" t="n">
         <v>-5658</v>
       </c>
-      <c r="E35" s="29" t="n">
+      <c r="E35" s="25" t="n">
         <v>1240</v>
       </c>
-      <c r="F35" s="29" t="n">
+      <c r="F35" s="25" t="n">
         <v>9654</v>
       </c>
     </row>
@@ -6125,16 +6398,16 @@
           <t>Other Income Expense</t>
         </is>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="25" t="n">
         <v>-45</v>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D36" s="25" t="n">
         <v>-333</v>
       </c>
-      <c r="E36" s="29" t="n">
+      <c r="E36" s="25" t="n">
         <v>-32</v>
       </c>
-      <c r="F36" s="29" t="n">
+      <c r="F36" s="25" t="n">
         <v>-174</v>
       </c>
     </row>
@@ -6144,16 +6417,16 @@
           <t>Other Non Operating Income Expenses</t>
         </is>
       </c>
-      <c r="C37" s="29" t="n">
+      <c r="C37" s="25" t="n">
         <v>19</v>
       </c>
-      <c r="D37" s="29" t="n">
+      <c r="D37" s="25" t="n">
         <v>-3</v>
       </c>
-      <c r="E37" s="29" t="n">
+      <c r="E37" s="25" t="n">
         <v>-17</v>
       </c>
-      <c r="F37" s="29" t="n">
+      <c r="F37" s="25" t="n">
         <v>-4</v>
       </c>
     </row>
@@ -6163,16 +6436,16 @@
           <t>Special Income Charges</t>
         </is>
       </c>
-      <c r="C38" s="29" t="n">
+      <c r="C38" s="25" t="n">
         <v>-90</v>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D38" s="25" t="n">
         <v>-340</v>
       </c>
-      <c r="E38" s="29" t="n">
+      <c r="E38" s="25" t="n">
         <v>-2</v>
       </c>
-      <c r="F38" s="29" t="n">
+      <c r="F38" s="25" t="n">
         <v>-98</v>
       </c>
     </row>
@@ -6182,16 +6455,16 @@
           <t>Gain On Sale Of Ppe</t>
         </is>
       </c>
-      <c r="B39" s="29" t="n">
+      <c r="B39" s="25" t="n">
         <v>24</v>
       </c>
-      <c r="C39" s="29" t="n">
+      <c r="C39" s="25" t="n">
         <v>41</v>
       </c>
-      <c r="D39" s="29" t="n">
+      <c r="D39" s="25" t="n">
         <v>54</v>
       </c>
-      <c r="E39" s="29" t="n">
+      <c r="E39" s="25" t="n">
         <v>59</v>
       </c>
     </row>
@@ -6201,16 +6474,16 @@
           <t>Other Special Charges</t>
         </is>
       </c>
-      <c r="B40" s="29" t="n">
+      <c r="B40" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="C40" s="29" t="n">
+      <c r="C40" s="25" t="n">
         <v>83</v>
       </c>
-      <c r="D40" s="29" t="n">
+      <c r="D40" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="F40" s="29" t="n">
+      <c r="F40" s="25" t="n">
         <v>59</v>
       </c>
     </row>
@@ -6220,16 +6493,16 @@
           <t>Write Off</t>
         </is>
       </c>
-      <c r="C41" s="29" t="n">
+      <c r="C41" s="25" t="n">
         <v>63</v>
       </c>
-      <c r="D41" s="29" t="n">
+      <c r="D41" s="25" t="n">
         <v>14</v>
       </c>
-      <c r="E41" s="29" t="n">
+      <c r="E41" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="29" t="n">
+      <c r="F41" s="25" t="n">
         <v>9</v>
       </c>
     </row>
@@ -6239,16 +6512,16 @@
           <t>Impairment Of Capital Assets</t>
         </is>
       </c>
-      <c r="C42" s="29" t="n">
+      <c r="C42" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D42" s="29" t="n">
+      <c r="D42" s="25" t="n">
         <v>101</v>
       </c>
-      <c r="E42" s="29" t="n">
+      <c r="E42" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F42" s="29" t="n">
+      <c r="F42" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6258,16 +6531,16 @@
           <t>Restructuring And Mergern Acquisition</t>
         </is>
       </c>
-      <c r="C43" s="29" t="n">
+      <c r="C43" s="25" t="n">
         <v>-15</v>
       </c>
-      <c r="D43" s="29" t="n">
+      <c r="D43" s="25" t="n">
         <v>157</v>
       </c>
-      <c r="E43" s="29" t="n">
+      <c r="E43" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F43" s="29" t="n">
+      <c r="F43" s="25" t="n">
         <v>30</v>
       </c>
     </row>
@@ -6277,16 +6550,16 @@
           <t>Gain On Sale Of Security</t>
         </is>
       </c>
-      <c r="B44" s="29" t="n">
+      <c r="B44" s="25" t="n">
         <v>82</v>
       </c>
-      <c r="C44" s="29" t="n">
+      <c r="C44" s="25" t="n">
         <v>26</v>
       </c>
-      <c r="D44" s="29" t="n">
+      <c r="D44" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="F44" s="29" t="n">
+      <c r="F44" s="25" t="n">
         <v>-72</v>
       </c>
     </row>
@@ -6296,16 +6569,16 @@
           <t>Net Non Operating Interest Income Expense</t>
         </is>
       </c>
-      <c r="C45" s="29" t="n">
+      <c r="C45" s="25" t="n">
         <v>-93</v>
       </c>
-      <c r="D45" s="29" t="n">
+      <c r="D45" s="25" t="n">
         <v>80</v>
       </c>
-      <c r="E45" s="29" t="n">
+      <c r="E45" s="25" t="n">
         <v>-33</v>
       </c>
-      <c r="F45" s="29" t="n">
+      <c r="F45" s="25" t="n">
         <v>19</v>
       </c>
     </row>
@@ -6315,16 +6588,16 @@
           <t>Interest Expense Non Operating</t>
         </is>
       </c>
-      <c r="C46" s="29" t="n">
+      <c r="C46" s="25" t="n">
         <v>189</v>
       </c>
-      <c r="D46" s="29" t="n">
+      <c r="D46" s="25" t="n">
         <v>388</v>
       </c>
-      <c r="E46" s="29" t="n">
+      <c r="E46" s="25" t="n">
         <v>562</v>
       </c>
-      <c r="F46" s="29" t="n">
+      <c r="F46" s="25" t="n">
         <v>477</v>
       </c>
     </row>
@@ -6334,16 +6607,16 @@
           <t>Interest Income Non Operating</t>
         </is>
       </c>
-      <c r="C47" s="29" t="n">
+      <c r="C47" s="25" t="n">
         <v>96</v>
       </c>
-      <c r="D47" s="29" t="n">
+      <c r="D47" s="25" t="n">
         <v>468</v>
       </c>
-      <c r="E47" s="29" t="n">
+      <c r="E47" s="25" t="n">
         <v>529</v>
       </c>
-      <c r="F47" s="29" t="n">
+      <c r="F47" s="25" t="n">
         <v>496</v>
       </c>
     </row>
@@ -6353,16 +6626,16 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="C48" s="29" t="n">
+      <c r="C48" s="25" t="n">
         <v>9709</v>
       </c>
-      <c r="D48" s="29" t="n">
+      <c r="D48" s="25" t="n">
         <v>-5405</v>
       </c>
-      <c r="E48" s="29" t="n">
+      <c r="E48" s="25" t="n">
         <v>1305</v>
       </c>
-      <c r="F48" s="29" t="n">
+      <c r="F48" s="25" t="n">
         <v>9809</v>
       </c>
     </row>
@@ -6372,16 +6645,16 @@
           <t>Operating Expense</t>
         </is>
       </c>
-      <c r="C49" s="29" t="n">
+      <c r="C49" s="25" t="n">
         <v>4189</v>
       </c>
-      <c r="D49" s="29" t="n">
+      <c r="D49" s="25" t="n">
         <v>3989</v>
       </c>
-      <c r="E49" s="29" t="n">
+      <c r="E49" s="25" t="n">
         <v>4308</v>
       </c>
-      <c r="F49" s="29" t="n">
+      <c r="F49" s="25" t="n">
         <v>5064</v>
       </c>
     </row>
@@ -6391,16 +6664,16 @@
           <t>Other Operating Expenses</t>
         </is>
       </c>
-      <c r="C50" s="29" t="n">
+      <c r="C50" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="D50" s="29" t="n">
+      <c r="D50" s="25" t="n">
         <v>-45</v>
       </c>
-      <c r="E50" s="29" t="n">
+      <c r="E50" s="25" t="n">
         <v>-251</v>
       </c>
-      <c r="F50" s="29" t="n">
+      <c r="F50" s="25" t="n">
         <v>61</v>
       </c>
     </row>
@@ -6410,16 +6683,16 @@
           <t>Research And Development</t>
         </is>
       </c>
-      <c r="C51" s="29" t="n">
+      <c r="C51" s="25" t="n">
         <v>3116</v>
       </c>
-      <c r="D51" s="29" t="n">
+      <c r="D51" s="25" t="n">
         <v>3114</v>
       </c>
-      <c r="E51" s="29" t="n">
+      <c r="E51" s="25" t="n">
         <v>3430</v>
       </c>
-      <c r="F51" s="29" t="n">
+      <c r="F51" s="25" t="n">
         <v>3798</v>
       </c>
     </row>
@@ -6429,16 +6702,16 @@
           <t>Selling General And Administration</t>
         </is>
       </c>
-      <c r="C52" s="29" t="n">
+      <c r="C52" s="25" t="n">
         <v>1066</v>
       </c>
-      <c r="D52" s="29" t="n">
+      <c r="D52" s="25" t="n">
         <v>920</v>
       </c>
-      <c r="E52" s="29" t="n">
+      <c r="E52" s="25" t="n">
         <v>1129</v>
       </c>
-      <c r="F52" s="29" t="n">
+      <c r="F52" s="25" t="n">
         <v>1205</v>
       </c>
     </row>
@@ -6448,16 +6721,16 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="C53" s="29" t="n">
+      <c r="C53" s="25" t="n">
         <v>13898</v>
       </c>
-      <c r="D53" s="29" t="n">
+      <c r="D53" s="25" t="n">
         <v>-1416</v>
       </c>
-      <c r="E53" s="29" t="n">
+      <c r="E53" s="25" t="n">
         <v>5613</v>
       </c>
-      <c r="F53" s="29" t="n">
+      <c r="F53" s="25" t="n">
         <v>14873</v>
       </c>
     </row>
@@ -6467,16 +6740,16 @@
           <t>Cost Of Revenue</t>
         </is>
       </c>
-      <c r="C54" s="29" t="n">
+      <c r="C54" s="25" t="n">
         <v>16860</v>
       </c>
-      <c r="D54" s="29" t="n">
+      <c r="D54" s="25" t="n">
         <v>16956</v>
       </c>
-      <c r="E54" s="29" t="n">
+      <c r="E54" s="25" t="n">
         <v>19498</v>
       </c>
-      <c r="F54" s="29" t="n">
+      <c r="F54" s="25" t="n">
         <v>22505</v>
       </c>
     </row>
@@ -6486,16 +6759,16 @@
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="C55" s="29" t="n">
+      <c r="C55" s="25" t="n">
         <v>30758</v>
       </c>
-      <c r="D55" s="29" t="n">
+      <c r="D55" s="25" t="n">
         <v>15540</v>
       </c>
-      <c r="E55" s="29" t="n">
+      <c r="E55" s="25" t="n">
         <v>25111</v>
       </c>
-      <c r="F55" s="29" t="n">
+      <c r="F55" s="25" t="n">
         <v>37378</v>
       </c>
     </row>
@@ -6505,16 +6778,16 @@
           <t>Operating Revenue</t>
         </is>
       </c>
-      <c r="C56" s="29" t="n">
+      <c r="C56" s="25" t="n">
         <v>30758</v>
       </c>
-      <c r="D56" s="29" t="n">
+      <c r="D56" s="25" t="n">
         <v>15540</v>
       </c>
-      <c r="E56" s="29" t="n">
+      <c r="E56" s="25" t="n">
         <v>25111</v>
       </c>
-      <c r="F56" s="29" t="n">
+      <c r="F56" s="25" t="n">
         <v>37378</v>
       </c>
     </row>

--- a/docs/reports/MU.xlsx
+++ b/docs/reports/MU.xlsx
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>1264.833590981985</v>
+        <v>1275.101790010158</v>
       </c>
     </row>
     <row r="8">
@@ -3219,13 +3219,13 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>490.5879139380186</v>
+        <v>544.0424299313142</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>411.2563747263457</v>
+        <v>455.9623309573281</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>582.4683357171762</v>
+        <v>646.0592762573693</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>0.2028985507246377</v>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>1264.833590981985</v>
+        <v>1275.101790010158</v>
       </c>
     </row>
     <row r="20">
@@ -3415,7 +3415,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Target anchored 15% to the Street consensus ($1,486.00); model-only target $1,225.80.</t>
+          <t>Target anchored 15% to the Street consensus ($1,486.00); model-only target $1,237.88.</t>
         </is>
       </c>
     </row>
@@ -3530,28 +3530,28 @@
         <v>234240</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>258619.8028564394</v>
+        <v>267895.7660522531</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>279149.0796650785</v>
+        <v>299823.6538162798</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>296566.539726581</v>
+        <v>328800.2167485189</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>311606.8470605715</v>
+        <v>353876.244728822</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>324907.1385926625</v>
+        <v>374506.4339964138</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>336980.6129812768</v>
+        <v>390657.0239625092</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>348222.8721527889</v>
+        <v>402926.840402853</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>356928.4439566086</v>
+        <v>413000.0114129243</v>
       </c>
     </row>
     <row r="6">
@@ -3699,28 +3699,28 @@
         <v>169002.39111564</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>90251.46527010441</v>
+        <v>93502.37224080326</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>88346.6223310115</v>
+        <v>94918.40554576644</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>84215.6520223738</v>
+        <v>93410.95537205391</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>78348.49884989558</v>
+        <v>89028.80289088754</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>71117.85032809456</v>
+        <v>82033.38744706126</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>62790.08135416255</v>
+        <v>72853.15361879196</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>64897.74213834155</v>
+        <v>75153.45736965357</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>66529.83334126099</v>
+        <v>77041.94145335582</v>
       </c>
     </row>
     <row r="10">
@@ -3783,28 +3783,28 @@
         <v>59492.03935788296</v>
       </c>
       <c r="D12" s="20" t="n">
-        <v>67143.9585526841</v>
+        <v>68826.67163645057</v>
       </c>
       <c r="E12" s="20" t="n">
-        <v>65886.41222891305</v>
+        <v>69925.38235889467</v>
       </c>
       <c r="F12" s="20" t="n">
-        <v>62836.08219156035</v>
+        <v>68856.9745145253</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>58373.33348664458</v>
+        <v>65640.35089070222</v>
       </c>
       <c r="H12" s="20" t="n">
-        <v>52795.41335332842</v>
+        <v>60447.51095683</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>46319.25506899595</v>
+        <v>53569.18475438456</v>
       </c>
       <c r="J12" s="20" t="n">
-        <v>50446.45970531934</v>
+        <v>58496.95185811818</v>
       </c>
       <c r="K12" s="20" t="n">
-        <v>54487.19885313424</v>
+        <v>63107.47289180101</v>
       </c>
     </row>
     <row r="13">
@@ -4141,25 +4141,25 @@
         <v>0.8075468786171773</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.1040804425223677</v>
+        <v>0.1436806952367359</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.07938014251768261</v>
+        <v>0.1191802626615577</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.06239483247589359</v>
+        <v>0.09664535323818985</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.05071478174124758</v>
+        <v>0.07626524163602469</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0.04268292451707791</v>
+        <v>0.05829775119095883</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0.03715976952956648</v>
+        <v>0.043125</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>0.03336173874233148</v>
+        <v>0.03140815520450309</v>
       </c>
       <c r="K26" s="11" t="n">
         <v>0.025</v>
